--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY126"/>
+  <dimension ref="A1:AY125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11000,7 +11000,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135326366</v>
+        <v>135326496</v>
       </c>
       <c r="B95" t="n">
         <v>57975</v>
@@ -11039,17 +11039,17 @@
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>621323</v>
+        <v>621246</v>
       </c>
       <c r="R95" t="n">
-        <v>7322015</v>
+        <v>7321956</v>
       </c>
       <c r="S95" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11088,12 +11088,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11108,12 +11108,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11124,7 +11124,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135326496</v>
+        <v>135326497</v>
       </c>
       <c r="B96" t="n">
         <v>57975</v>
@@ -11167,13 +11167,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>621246</v>
+        <v>621165</v>
       </c>
       <c r="R96" t="n">
-        <v>7321956</v>
+        <v>7322002</v>
       </c>
       <c r="S96" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -11248,7 +11248,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135326497</v>
+        <v>135329838</v>
       </c>
       <c r="B97" t="n">
         <v>57975</v>
@@ -11277,27 +11277,19 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>621165</v>
+        <v>621123</v>
       </c>
       <c r="R97" t="n">
-        <v>7322002</v>
+        <v>7322113</v>
       </c>
       <c r="S97" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11326,7 +11318,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11336,12 +11328,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11356,12 +11348,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11372,7 +11364,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135329838</v>
+        <v>135329861</v>
       </c>
       <c r="B98" t="n">
         <v>57975</v>
@@ -11407,10 +11399,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>621123</v>
+        <v>621226</v>
       </c>
       <c r="R98" t="n">
-        <v>7322113</v>
+        <v>7322073</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11442,7 +11434,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11452,7 +11444,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -11488,7 +11480,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135329861</v>
+        <v>135330957</v>
       </c>
       <c r="B99" t="n">
         <v>57975</v>
@@ -11517,19 +11509,24 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>621226</v>
+        <v>621320</v>
       </c>
       <c r="R99" t="n">
-        <v>7322073</v>
+        <v>7322249</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11558,7 +11555,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11568,12 +11565,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11588,12 +11585,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11604,7 +11601,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135330957</v>
+        <v>135330964</v>
       </c>
       <c r="B100" t="n">
         <v>57975</v>
@@ -11633,24 +11630,27 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>621320</v>
+        <v>621397</v>
       </c>
       <c r="R100" t="n">
-        <v>7322249</v>
+        <v>7322108</v>
       </c>
       <c r="S100" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11689,12 +11689,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11725,7 +11725,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135330964</v>
+        <v>135330965</v>
       </c>
       <c r="B101" t="n">
         <v>57975</v>
@@ -11768,13 +11768,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>621397</v>
+        <v>621436</v>
       </c>
       <c r="R101" t="n">
-        <v>7322108</v>
+        <v>7322109</v>
       </c>
       <c r="S101" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -11849,7 +11849,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135330965</v>
+        <v>135330966</v>
       </c>
       <c r="B102" t="n">
         <v>57975</v>
@@ -11882,7 +11882,7 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>621436</v>
+        <v>621459</v>
       </c>
       <c r="R102" t="n">
-        <v>7322109</v>
+        <v>7322135</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11937,12 +11937,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11973,7 +11973,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135330966</v>
+        <v>135330967</v>
       </c>
       <c r="B103" t="n">
         <v>57975</v>
@@ -12006,7 +12006,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -12016,13 +12016,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>621459</v>
+        <v>621219</v>
       </c>
       <c r="R103" t="n">
-        <v>7322135</v>
+        <v>7322131</v>
       </c>
       <c r="S103" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12061,12 +12061,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spår av födosök</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12097,40 +12097,44 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135330967</v>
+        <v>135330945</v>
       </c>
       <c r="B104" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -12140,13 +12144,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>621219</v>
+        <v>621163</v>
       </c>
       <c r="R104" t="n">
-        <v>7322131</v>
+        <v>7322161</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12175,7 +12179,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12185,12 +12189,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Spår av födosök</t>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12221,60 +12225,48 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135330945</v>
+        <v>135326371</v>
       </c>
       <c r="B105" t="n">
-        <v>57162</v>
+        <v>58136</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>621163</v>
+        <v>621395</v>
       </c>
       <c r="R105" t="n">
-        <v>7322161</v>
+        <v>7322009</v>
       </c>
       <c r="S105" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12303,7 +12295,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12313,12 +12305,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12333,12 +12320,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -12349,10 +12336,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135326371</v>
+        <v>135326513</v>
       </c>
       <c r="B106" t="n">
-        <v>58136</v>
+        <v>41606</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12360,37 +12347,41 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>215713</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>621395</v>
+        <v>621171</v>
       </c>
       <c r="R106" t="n">
-        <v>7322009</v>
+        <v>7322040</v>
       </c>
       <c r="S106" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12419,7 +12410,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12429,7 +12420,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12444,12 +12435,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -12460,49 +12451,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135326513</v>
+        <v>135326512</v>
       </c>
       <c r="B107" t="n">
-        <v>41606</v>
+        <v>98066</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>215713</v>
+        <v>221941</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>621171</v>
+        <v>621161</v>
       </c>
       <c r="R107" t="n">
-        <v>7322040</v>
+        <v>7322070</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12534,7 +12521,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12544,7 +12531,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12575,48 +12562,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135326512</v>
+        <v>135326487</v>
       </c>
       <c r="B108" t="n">
-        <v>98066</v>
+        <v>78382</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221941</v>
+        <v>228579</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>621161</v>
+        <v>621204</v>
       </c>
       <c r="R108" t="n">
-        <v>7322070</v>
+        <v>7322016</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12645,7 +12632,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12655,7 +12642,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12670,12 +12657,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12686,7 +12673,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135326487</v>
+        <v>135326521</v>
       </c>
       <c r="B109" t="n">
         <v>78382</v>
@@ -12717,17 +12704,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>621204</v>
+        <v>621266</v>
       </c>
       <c r="R109" t="n">
-        <v>7322016</v>
+        <v>7322030</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12756,7 +12743,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12766,7 +12753,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12781,12 +12768,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -12797,7 +12784,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135326521</v>
+        <v>135326526</v>
       </c>
       <c r="B110" t="n">
         <v>78382</v>
@@ -12832,10 +12819,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>621266</v>
+        <v>621284</v>
       </c>
       <c r="R110" t="n">
-        <v>7322030</v>
+        <v>7322006</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12867,7 +12854,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12877,7 +12864,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12908,10 +12895,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135326526</v>
+        <v>135326483</v>
       </c>
       <c r="B111" t="n">
-        <v>78382</v>
+        <v>79396</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12919,37 +12906,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228579</v>
+        <v>260591</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>621284</v>
+        <v>621165</v>
       </c>
       <c r="R111" t="n">
-        <v>7322006</v>
+        <v>7322074</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12978,7 +12965,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12988,7 +12975,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13003,12 +12990,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -13019,10 +13006,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135326483</v>
+        <v>135325606</v>
       </c>
       <c r="B112" t="n">
-        <v>79396</v>
+        <v>92245</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13030,37 +13017,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>260591</v>
+        <v>658</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>621165</v>
+        <v>621546</v>
       </c>
       <c r="R112" t="n">
-        <v>7322074</v>
+        <v>7322049</v>
       </c>
       <c r="S112" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13089,7 +13076,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13099,7 +13086,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13114,12 +13101,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -13130,10 +13117,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135325606</v>
+        <v>135323160</v>
       </c>
       <c r="B113" t="n">
-        <v>92245</v>
+        <v>79452</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13141,37 +13128,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>621546</v>
+        <v>621529</v>
       </c>
       <c r="R113" t="n">
-        <v>7322049</v>
+        <v>7322033</v>
       </c>
       <c r="S113" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13200,7 +13187,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13210,7 +13197,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13225,12 +13212,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -13241,32 +13228,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135323160</v>
+        <v>135323154</v>
       </c>
       <c r="B114" t="n">
-        <v>79452</v>
+        <v>92795</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>864</v>
+        <v>918</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13276,13 +13263,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>621529</v>
+        <v>621513</v>
       </c>
       <c r="R114" t="n">
-        <v>7322033</v>
+        <v>7322084</v>
       </c>
       <c r="S114" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13311,7 +13298,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13321,7 +13308,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13352,7 +13339,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135323154</v>
+        <v>135323161</v>
       </c>
       <c r="B115" t="n">
         <v>92795</v>
@@ -13387,10 +13374,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>621513</v>
+        <v>621535</v>
       </c>
       <c r="R115" t="n">
-        <v>7322084</v>
+        <v>7322033</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13422,7 +13409,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13432,7 +13419,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13463,7 +13450,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135323161</v>
+        <v>135325607</v>
       </c>
       <c r="B116" t="n">
         <v>92795</v>
@@ -13494,14 +13481,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>621535</v>
+        <v>621551</v>
       </c>
       <c r="R116" t="n">
-        <v>7322033</v>
+        <v>7322047</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13533,7 +13520,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13543,7 +13530,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13558,12 +13545,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -13574,7 +13561,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135325607</v>
+        <v>135325611</v>
       </c>
       <c r="B117" t="n">
         <v>92795</v>
@@ -13609,13 +13596,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>621551</v>
+        <v>621536</v>
       </c>
       <c r="R117" t="n">
-        <v>7322047</v>
+        <v>7322045</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13644,7 +13631,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13654,7 +13641,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13685,32 +13672,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135325611</v>
+        <v>135325610</v>
       </c>
       <c r="B118" t="n">
-        <v>92795</v>
+        <v>91970</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>918</v>
+        <v>1108</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13720,13 +13707,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>621536</v>
+        <v>621539</v>
       </c>
       <c r="R118" t="n">
-        <v>7322045</v>
+        <v>7322038</v>
       </c>
       <c r="S118" t="n">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13755,7 +13742,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13765,7 +13752,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13796,10 +13783,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135325610</v>
+        <v>135325608</v>
       </c>
       <c r="B119" t="n">
-        <v>91970</v>
+        <v>91974</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13807,21 +13794,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13831,13 +13818,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>621539</v>
+        <v>621550</v>
       </c>
       <c r="R119" t="n">
-        <v>7322038</v>
+        <v>7322047</v>
       </c>
       <c r="S119" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13866,7 +13853,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13876,7 +13863,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13907,10 +13894,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135325608</v>
+        <v>135325601</v>
       </c>
       <c r="B120" t="n">
-        <v>91974</v>
+        <v>83222</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13918,21 +13905,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13942,13 +13929,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>621550</v>
+        <v>621522</v>
       </c>
       <c r="R120" t="n">
-        <v>7322047</v>
+        <v>7322095</v>
       </c>
       <c r="S120" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13977,7 +13964,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13987,7 +13974,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Cinnoberflamlav</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14018,7 +14010,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135325601</v>
+        <v>135325603</v>
       </c>
       <c r="B121" t="n">
         <v>83222</v>
@@ -14053,10 +14045,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>621522</v>
+        <v>621524</v>
       </c>
       <c r="R121" t="n">
-        <v>7322095</v>
+        <v>7322055</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14088,7 +14080,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14098,12 +14090,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Cinnoberflamlav</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14134,48 +14121,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135325603</v>
+        <v>135323155</v>
       </c>
       <c r="B122" t="n">
-        <v>83222</v>
+        <v>79373</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>621524</v>
+        <v>621518</v>
       </c>
       <c r="R122" t="n">
-        <v>7322055</v>
+        <v>7322064</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14229,12 +14216,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -14245,48 +14232,48 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135323155</v>
+        <v>135325602</v>
       </c>
       <c r="B123" t="n">
-        <v>79373</v>
+        <v>83358</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>621518</v>
+        <v>621515</v>
       </c>
       <c r="R123" t="n">
-        <v>7322064</v>
+        <v>7322081</v>
       </c>
       <c r="S123" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14315,7 +14302,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14325,7 +14312,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14340,12 +14327,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -14356,7 +14343,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135325602</v>
+        <v>135325609</v>
       </c>
       <c r="B124" t="n">
         <v>83358</v>
@@ -14391,13 +14378,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>621515</v>
+        <v>621545</v>
       </c>
       <c r="R124" t="n">
-        <v>7322081</v>
+        <v>7322048</v>
       </c>
       <c r="S124" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14426,7 +14413,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14436,7 +14423,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14467,48 +14454,48 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135325609</v>
+        <v>135323153</v>
       </c>
       <c r="B125" t="n">
-        <v>83358</v>
+        <v>78731</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6440</v>
+        <v>6443</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>621545</v>
+        <v>621513</v>
       </c>
       <c r="R125" t="n">
-        <v>7322048</v>
+        <v>7322084</v>
       </c>
       <c r="S125" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14537,7 +14524,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14547,7 +14534,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>På torr grangren</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14562,131 +14554,15 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>135323153</v>
-      </c>
-      <c r="B126" t="n">
-        <v>78731</v>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E126" t="n">
-        <v>6443</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Sotlav</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Acolium inquinans</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>(Sm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>Skornjamyran, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q126" t="n">
-        <v>621513</v>
-      </c>
-      <c r="R126" t="n">
-        <v>7322084</v>
-      </c>
-      <c r="S126" t="n">
-        <v>5</v>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>På torr grangren</t>
-        </is>
-      </c>
-      <c r="AD126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT126" t="inlineStr"/>
-      <c r="AW126" t="inlineStr">
-        <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY125"/>
+  <dimension ref="A1:AY126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11000,7 +11000,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135326496</v>
+        <v>135326366</v>
       </c>
       <c r="B95" t="n">
         <v>57975</v>
@@ -11039,17 +11039,17 @@
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>621246</v>
+        <v>621323</v>
       </c>
       <c r="R95" t="n">
-        <v>7321956</v>
+        <v>7322015</v>
       </c>
       <c r="S95" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11088,12 +11088,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11108,12 +11108,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11124,7 +11124,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135326497</v>
+        <v>135326496</v>
       </c>
       <c r="B96" t="n">
         <v>57975</v>
@@ -11167,13 +11167,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>621165</v>
+        <v>621246</v>
       </c>
       <c r="R96" t="n">
-        <v>7322002</v>
+        <v>7321956</v>
       </c>
       <c r="S96" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -11248,7 +11248,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135329838</v>
+        <v>135326497</v>
       </c>
       <c r="B97" t="n">
         <v>57975</v>
@@ -11277,19 +11277,27 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>621123</v>
+        <v>621165</v>
       </c>
       <c r="R97" t="n">
-        <v>7322113</v>
+        <v>7322002</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11318,7 +11326,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11328,12 +11336,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11348,12 +11356,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11364,7 +11372,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135329861</v>
+        <v>135329838</v>
       </c>
       <c r="B98" t="n">
         <v>57975</v>
@@ -11399,10 +11407,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>621226</v>
+        <v>621123</v>
       </c>
       <c r="R98" t="n">
-        <v>7322073</v>
+        <v>7322113</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11434,7 +11442,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11444,7 +11452,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -11480,7 +11488,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135330957</v>
+        <v>135329861</v>
       </c>
       <c r="B99" t="n">
         <v>57975</v>
@@ -11509,24 +11517,19 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>621320</v>
+        <v>621226</v>
       </c>
       <c r="R99" t="n">
-        <v>7322249</v>
+        <v>7322073</v>
       </c>
       <c r="S99" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11555,7 +11558,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11565,12 +11568,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11585,12 +11588,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11601,7 +11604,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135330964</v>
+        <v>135330957</v>
       </c>
       <c r="B100" t="n">
         <v>57975</v>
@@ -11630,27 +11633,24 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>621397</v>
+        <v>621320</v>
       </c>
       <c r="R100" t="n">
-        <v>7322108</v>
+        <v>7322249</v>
       </c>
       <c r="S100" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11689,12 +11689,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11725,7 +11725,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135330965</v>
+        <v>135330964</v>
       </c>
       <c r="B101" t="n">
         <v>57975</v>
@@ -11768,13 +11768,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>621436</v>
+        <v>621397</v>
       </c>
       <c r="R101" t="n">
-        <v>7322109</v>
+        <v>7322108</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -11849,7 +11849,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135330966</v>
+        <v>135330965</v>
       </c>
       <c r="B102" t="n">
         <v>57975</v>
@@ -11882,7 +11882,7 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>621459</v>
+        <v>621436</v>
       </c>
       <c r="R102" t="n">
-        <v>7322135</v>
+        <v>7322109</v>
       </c>
       <c r="S102" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11937,12 +11937,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11973,7 +11973,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135330967</v>
+        <v>135330966</v>
       </c>
       <c r="B103" t="n">
         <v>57975</v>
@@ -12006,7 +12006,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -12016,13 +12016,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>621219</v>
+        <v>621459</v>
       </c>
       <c r="R103" t="n">
-        <v>7322131</v>
+        <v>7322135</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12061,12 +12061,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Spår av födosök</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12097,44 +12097,40 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135330945</v>
+        <v>135330967</v>
       </c>
       <c r="B104" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -12144,13 +12140,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>621163</v>
+        <v>621219</v>
       </c>
       <c r="R104" t="n">
-        <v>7322161</v>
+        <v>7322131</v>
       </c>
       <c r="S104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12179,7 +12175,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12189,12 +12185,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Uppflygande</t>
+          <t>Spår av födosök</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12225,48 +12221,60 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135326371</v>
+        <v>135330945</v>
       </c>
       <c r="B105" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>621395</v>
+        <v>621163</v>
       </c>
       <c r="R105" t="n">
-        <v>7322009</v>
+        <v>7322161</v>
       </c>
       <c r="S105" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12295,7 +12303,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12305,7 +12313,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12320,12 +12333,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -12336,10 +12349,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135326513</v>
+        <v>135326371</v>
       </c>
       <c r="B106" t="n">
-        <v>41606</v>
+        <v>58136</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12347,41 +12360,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>215713</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>621171</v>
+        <v>621395</v>
       </c>
       <c r="R106" t="n">
-        <v>7322040</v>
+        <v>7322009</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12410,7 +12419,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12420,7 +12429,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12435,12 +12444,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -12451,45 +12460,49 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135326512</v>
+        <v>135326513</v>
       </c>
       <c r="B107" t="n">
-        <v>98066</v>
+        <v>41606</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221941</v>
+        <v>215713</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>621161</v>
+        <v>621171</v>
       </c>
       <c r="R107" t="n">
-        <v>7322070</v>
+        <v>7322040</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12521,7 +12534,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12531,7 +12544,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12562,48 +12575,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135326487</v>
+        <v>135326512</v>
       </c>
       <c r="B108" t="n">
-        <v>78382</v>
+        <v>98066</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228579</v>
+        <v>221941</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>621204</v>
+        <v>621161</v>
       </c>
       <c r="R108" t="n">
-        <v>7322016</v>
+        <v>7322070</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12632,7 +12645,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12642,7 +12655,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12657,12 +12670,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12673,7 +12686,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135326521</v>
+        <v>135326487</v>
       </c>
       <c r="B109" t="n">
         <v>78382</v>
@@ -12704,17 +12717,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>621266</v>
+        <v>621204</v>
       </c>
       <c r="R109" t="n">
-        <v>7322030</v>
+        <v>7322016</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12743,7 +12756,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12753,7 +12766,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12768,12 +12781,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -12784,7 +12797,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135326526</v>
+        <v>135326521</v>
       </c>
       <c r="B110" t="n">
         <v>78382</v>
@@ -12819,10 +12832,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>621284</v>
+        <v>621266</v>
       </c>
       <c r="R110" t="n">
-        <v>7322006</v>
+        <v>7322030</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12854,7 +12867,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12864,7 +12877,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12895,10 +12908,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135326483</v>
+        <v>135326526</v>
       </c>
       <c r="B111" t="n">
-        <v>79396</v>
+        <v>78382</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12906,37 +12919,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>260591</v>
+        <v>228579</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>621165</v>
+        <v>621284</v>
       </c>
       <c r="R111" t="n">
-        <v>7322074</v>
+        <v>7322006</v>
       </c>
       <c r="S111" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12965,7 +12978,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12975,7 +12988,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12990,12 +13003,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -13006,10 +13019,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135325606</v>
+        <v>135326483</v>
       </c>
       <c r="B112" t="n">
-        <v>92245</v>
+        <v>79396</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13017,37 +13030,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>658</v>
+        <v>260591</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>621546</v>
+        <v>621165</v>
       </c>
       <c r="R112" t="n">
-        <v>7322049</v>
+        <v>7322074</v>
       </c>
       <c r="S112" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13076,7 +13089,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13086,7 +13099,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13101,12 +13114,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -13117,10 +13130,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135323160</v>
+        <v>135325606</v>
       </c>
       <c r="B113" t="n">
-        <v>79452</v>
+        <v>92245</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13128,37 +13141,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>621529</v>
+        <v>621546</v>
       </c>
       <c r="R113" t="n">
-        <v>7322033</v>
+        <v>7322049</v>
       </c>
       <c r="S113" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13187,7 +13200,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13197,7 +13210,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13212,12 +13225,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -13228,32 +13241,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135323154</v>
+        <v>135323160</v>
       </c>
       <c r="B114" t="n">
-        <v>92795</v>
+        <v>79452</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>918</v>
+        <v>864</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13263,13 +13276,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>621513</v>
+        <v>621529</v>
       </c>
       <c r="R114" t="n">
-        <v>7322084</v>
+        <v>7322033</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13298,7 +13311,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13308,7 +13321,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13339,7 +13352,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135323161</v>
+        <v>135323154</v>
       </c>
       <c r="B115" t="n">
         <v>92795</v>
@@ -13374,10 +13387,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>621535</v>
+        <v>621513</v>
       </c>
       <c r="R115" t="n">
-        <v>7322033</v>
+        <v>7322084</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13409,7 +13422,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13419,7 +13432,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13450,7 +13463,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135325607</v>
+        <v>135323161</v>
       </c>
       <c r="B116" t="n">
         <v>92795</v>
@@ -13481,14 +13494,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>621551</v>
+        <v>621535</v>
       </c>
       <c r="R116" t="n">
-        <v>7322047</v>
+        <v>7322033</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13520,7 +13533,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13530,7 +13543,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13545,12 +13558,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -13561,7 +13574,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135325611</v>
+        <v>135325607</v>
       </c>
       <c r="B117" t="n">
         <v>92795</v>
@@ -13596,13 +13609,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>621536</v>
+        <v>621551</v>
       </c>
       <c r="R117" t="n">
-        <v>7322045</v>
+        <v>7322047</v>
       </c>
       <c r="S117" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13631,7 +13644,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13641,7 +13654,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13672,32 +13685,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135325610</v>
+        <v>135325611</v>
       </c>
       <c r="B118" t="n">
-        <v>91970</v>
+        <v>92795</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13707,13 +13720,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>621539</v>
+        <v>621536</v>
       </c>
       <c r="R118" t="n">
-        <v>7322038</v>
+        <v>7322045</v>
       </c>
       <c r="S118" t="n">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13742,7 +13755,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13752,7 +13765,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13783,10 +13796,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135325608</v>
+        <v>135325610</v>
       </c>
       <c r="B119" t="n">
-        <v>91974</v>
+        <v>91970</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13794,21 +13807,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13818,13 +13831,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>621550</v>
+        <v>621539</v>
       </c>
       <c r="R119" t="n">
-        <v>7322047</v>
+        <v>7322038</v>
       </c>
       <c r="S119" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13853,7 +13866,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13863,7 +13876,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13894,10 +13907,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135325601</v>
+        <v>135325608</v>
       </c>
       <c r="B120" t="n">
-        <v>83222</v>
+        <v>91974</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13905,21 +13918,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13929,13 +13942,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>621522</v>
+        <v>621550</v>
       </c>
       <c r="R120" t="n">
-        <v>7322095</v>
+        <v>7322047</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13964,7 +13977,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13974,12 +13987,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Cinnoberflamlav</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14010,7 +14018,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135325603</v>
+        <v>135325601</v>
       </c>
       <c r="B121" t="n">
         <v>83222</v>
@@ -14045,10 +14053,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>621524</v>
+        <v>621522</v>
       </c>
       <c r="R121" t="n">
-        <v>7322055</v>
+        <v>7322095</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14080,7 +14088,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14090,7 +14098,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Cinnoberflamlav</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14121,48 +14134,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135323155</v>
+        <v>135325603</v>
       </c>
       <c r="B122" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>621518</v>
+        <v>621524</v>
       </c>
       <c r="R122" t="n">
-        <v>7322064</v>
+        <v>7322055</v>
       </c>
       <c r="S122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14216,12 +14229,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -14232,48 +14245,48 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135325602</v>
+        <v>135323155</v>
       </c>
       <c r="B123" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>621515</v>
+        <v>621518</v>
       </c>
       <c r="R123" t="n">
-        <v>7322081</v>
+        <v>7322064</v>
       </c>
       <c r="S123" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14302,7 +14315,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14312,7 +14325,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14327,12 +14340,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -14343,7 +14356,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135325609</v>
+        <v>135325602</v>
       </c>
       <c r="B124" t="n">
         <v>83358</v>
@@ -14378,13 +14391,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>621545</v>
+        <v>621515</v>
       </c>
       <c r="R124" t="n">
-        <v>7322048</v>
+        <v>7322081</v>
       </c>
       <c r="S124" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14413,7 +14426,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14423,7 +14436,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14454,48 +14467,48 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135323153</v>
+        <v>135325609</v>
       </c>
       <c r="B125" t="n">
-        <v>78731</v>
+        <v>83358</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6443</v>
+        <v>6440</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>621513</v>
+        <v>621545</v>
       </c>
       <c r="R125" t="n">
-        <v>7322084</v>
+        <v>7322048</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14524,7 +14537,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14534,12 +14547,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>På torr grangren</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14554,15 +14562,131 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>135323153</v>
+      </c>
+      <c r="B126" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Sotlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Acolium inquinans</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Skornjamyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>621513</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7322084</v>
+      </c>
+      <c r="S126" t="n">
+        <v>5</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>På torr grangren</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
           <t>Cajsa Björkén</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
+      <c r="AX126" t="inlineStr">
         <is>
           <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
-      <c r="AY125" t="inlineStr">
+      <c r="AY126" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY126"/>
+  <dimension ref="A1:AY128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,48 +1013,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135323166</v>
+        <v>135360046</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>92201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>67</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621421</v>
+        <v>621248</v>
       </c>
       <c r="R5" t="n">
-        <v>7321969</v>
+        <v>7322029</v>
       </c>
       <c r="S5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,23 +1108,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135323172</v>
+        <v>135323166</v>
       </c>
       <c r="B6" t="n">
         <v>79039</v>
@@ -1159,13 +1155,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621355</v>
+        <v>621421</v>
       </c>
       <c r="R6" t="n">
-        <v>7321983</v>
+        <v>7321969</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,7 +1190,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,7 +1200,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1231,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135330954</v>
+        <v>135323172</v>
       </c>
       <c r="B7" t="n">
         <v>79039</v>
@@ -1266,14 +1262,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621277</v>
+        <v>621355</v>
       </c>
       <c r="R7" t="n">
-        <v>7322238</v>
+        <v>7321983</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1305,7 +1301,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1311,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,12 +1326,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1346,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135322209</v>
+        <v>135330954</v>
       </c>
       <c r="B8" t="n">
-        <v>92245</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,37 +1353,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>621279</v>
+        <v>621277</v>
       </c>
       <c r="R8" t="n">
-        <v>7322035</v>
+        <v>7322238</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,12 +1437,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1457,7 +1453,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135323170</v>
+        <v>135322209</v>
       </c>
       <c r="B9" t="n">
         <v>92245</v>
@@ -1488,17 +1484,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>621405</v>
+        <v>621279</v>
       </c>
       <c r="R9" t="n">
-        <v>7321964</v>
+        <v>7322035</v>
       </c>
       <c r="S9" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,12 +1548,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1568,7 +1564,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135323174</v>
+        <v>135323170</v>
       </c>
       <c r="B10" t="n">
         <v>92245</v>
@@ -1603,13 +1599,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>621335</v>
+        <v>621405</v>
       </c>
       <c r="R10" t="n">
-        <v>7321945</v>
+        <v>7321964</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1638,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1648,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,7 +1675,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135323544</v>
+        <v>135323174</v>
       </c>
       <c r="B11" t="n">
         <v>92245</v>
@@ -1710,14 +1706,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621325</v>
+        <v>621335</v>
       </c>
       <c r="R11" t="n">
-        <v>7322165</v>
+        <v>7321945</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1749,7 +1745,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1755,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,19 +1770,23 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135325614</v>
+        <v>135323544</v>
       </c>
       <c r="B12" t="n">
         <v>92245</v>
@@ -1817,14 +1817,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621499</v>
+        <v>621325</v>
       </c>
       <c r="R12" t="n">
-        <v>7322020</v>
+        <v>7322165</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,23 +1881,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135325615</v>
+        <v>135325614</v>
       </c>
       <c r="B13" t="n">
         <v>92245</v>
@@ -1932,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621477</v>
+        <v>621499</v>
       </c>
       <c r="R13" t="n">
-        <v>7322015</v>
+        <v>7322020</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1967,7 +1963,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1973,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,7 +2004,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135326363</v>
+        <v>135325615</v>
       </c>
       <c r="B14" t="n">
         <v>92245</v>
@@ -2039,17 +2035,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621274</v>
+        <v>621477</v>
       </c>
       <c r="R14" t="n">
-        <v>7322030</v>
+        <v>7322015</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2078,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2088,7 +2084,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,12 +2099,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2119,7 +2115,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135326494</v>
+        <v>135326363</v>
       </c>
       <c r="B15" t="n">
         <v>92245</v>
@@ -2150,17 +2146,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621284</v>
+        <v>621274</v>
       </c>
       <c r="R15" t="n">
-        <v>7321988</v>
+        <v>7322030</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2189,7 +2185,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2199,7 +2195,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2214,12 +2210,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2230,7 +2226,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135330944</v>
+        <v>135326494</v>
       </c>
       <c r="B16" t="n">
         <v>92245</v>
@@ -2261,17 +2257,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621163</v>
+        <v>621284</v>
       </c>
       <c r="R16" t="n">
-        <v>7322149</v>
+        <v>7321988</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2300,7 +2296,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2310,7 +2306,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,12 +2321,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2341,7 +2337,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135330962</v>
+        <v>135330944</v>
       </c>
       <c r="B17" t="n">
         <v>92245</v>
@@ -2376,13 +2372,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>621313</v>
+        <v>621163</v>
       </c>
       <c r="R17" t="n">
-        <v>7322173</v>
+        <v>7322149</v>
       </c>
       <c r="S17" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2411,7 +2407,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2421,7 +2417,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,10 +2448,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135323152</v>
+        <v>135330962</v>
       </c>
       <c r="B18" t="n">
-        <v>79452</v>
+        <v>92245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,37 +2459,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>621500</v>
+        <v>621313</v>
       </c>
       <c r="R18" t="n">
-        <v>7322090</v>
+        <v>7322173</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,7 +2518,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2528,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,12 +2543,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2563,7 +2559,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135326516</v>
+        <v>135323152</v>
       </c>
       <c r="B19" t="n">
         <v>79452</v>
@@ -2598,13 +2594,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621266</v>
+        <v>621500</v>
       </c>
       <c r="R19" t="n">
-        <v>7322033</v>
+        <v>7322090</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2633,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2643,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2658,12 +2654,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2674,7 +2670,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135329849</v>
+        <v>135326516</v>
       </c>
       <c r="B20" t="n">
         <v>79452</v>
@@ -2705,14 +2701,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>621260</v>
+        <v>621266</v>
       </c>
       <c r="R20" t="n">
-        <v>7322039</v>
+        <v>7322033</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2740,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2750,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2769,12 +2765,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2785,7 +2781,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135329856</v>
+        <v>135329849</v>
       </c>
       <c r="B21" t="n">
         <v>79452</v>
@@ -2820,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>621374</v>
+        <v>621260</v>
       </c>
       <c r="R21" t="n">
-        <v>7322008</v>
+        <v>7322039</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,7 +2851,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2861,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2896,7 +2892,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135329858</v>
+        <v>135329856</v>
       </c>
       <c r="B22" t="n">
         <v>79452</v>
@@ -2931,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>621401</v>
+        <v>621374</v>
       </c>
       <c r="R22" t="n">
-        <v>7322018</v>
+        <v>7322008</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2966,7 +2962,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2976,7 +2972,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,48 +3003,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135325596</v>
+        <v>135329858</v>
       </c>
       <c r="B23" t="n">
-        <v>92795</v>
+        <v>79452</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>918</v>
+        <v>864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>621469</v>
+        <v>621401</v>
       </c>
       <c r="R23" t="n">
-        <v>7322105</v>
+        <v>7322018</v>
       </c>
       <c r="S23" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3077,7 +3073,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3087,7 +3083,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3102,12 +3098,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3118,10 +3114,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135325619</v>
+        <v>135359947</v>
       </c>
       <c r="B24" t="n">
-        <v>92795</v>
+        <v>92689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,37 +3125,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>918</v>
+        <v>898</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>621430</v>
+        <v>621212</v>
       </c>
       <c r="R24" t="n">
-        <v>7321973</v>
+        <v>7321996</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3188,7 +3187,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3198,7 +3197,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3207,18 +3206,19 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3229,7 +3229,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135325628</v>
+        <v>135325596</v>
       </c>
       <c r="B25" t="n">
         <v>92795</v>
@@ -3264,13 +3264,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>621396</v>
+        <v>621469</v>
       </c>
       <c r="R25" t="n">
-        <v>7322008</v>
+        <v>7322105</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3340,7 +3340,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135326490</v>
+        <v>135325619</v>
       </c>
       <c r="B26" t="n">
         <v>92795</v>
@@ -3371,14 +3371,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>621245</v>
+        <v>621430</v>
       </c>
       <c r="R26" t="n">
-        <v>7322039</v>
+        <v>7321973</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3435,12 +3435,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3451,7 +3451,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135330955</v>
+        <v>135325628</v>
       </c>
       <c r="B27" t="n">
         <v>92795</v>
@@ -3482,17 +3482,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>621277</v>
+        <v>621396</v>
       </c>
       <c r="R27" t="n">
-        <v>7322229</v>
+        <v>7322008</v>
       </c>
       <c r="S27" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3546,12 +3546,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3562,48 +3562,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135323157</v>
+        <v>135326490</v>
       </c>
       <c r="B28" t="n">
-        <v>91970</v>
+        <v>92795</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>621507</v>
+        <v>621245</v>
       </c>
       <c r="R28" t="n">
-        <v>7322061</v>
+        <v>7322039</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3657,12 +3657,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3673,48 +3673,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135323537</v>
+        <v>135330955</v>
       </c>
       <c r="B29" t="n">
-        <v>91970</v>
+        <v>92795</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>621393</v>
+        <v>621277</v>
       </c>
       <c r="R29" t="n">
-        <v>7322163</v>
+        <v>7322229</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3768,19 +3768,23 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135323538</v>
+        <v>135323157</v>
       </c>
       <c r="B30" t="n">
         <v>91970</v>
@@ -3811,17 +3815,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>621368</v>
+        <v>621507</v>
       </c>
       <c r="R30" t="n">
-        <v>7322188</v>
+        <v>7322061</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3850,7 +3854,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3860,7 +3864,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3875,19 +3879,23 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135325613</v>
+        <v>135323537</v>
       </c>
       <c r="B31" t="n">
         <v>91970</v>
@@ -3918,17 +3926,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>621495</v>
+        <v>621393</v>
       </c>
       <c r="R31" t="n">
-        <v>7322020</v>
+        <v>7322163</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3957,7 +3965,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3967,7 +3975,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3982,23 +3990,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135325621</v>
+        <v>135323538</v>
       </c>
       <c r="B32" t="n">
         <v>91970</v>
@@ -4029,17 +4033,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>621385</v>
+        <v>621368</v>
       </c>
       <c r="R32" t="n">
-        <v>7321984</v>
+        <v>7322188</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4068,7 +4072,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4078,7 +4082,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4093,23 +4097,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135326368</v>
+        <v>135325613</v>
       </c>
       <c r="B33" t="n">
         <v>91970</v>
@@ -4140,17 +4140,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>621346</v>
+        <v>621495</v>
       </c>
       <c r="R33" t="n">
-        <v>7322011</v>
+        <v>7322020</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4204,12 +4204,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4220,7 +4220,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135329807</v>
+        <v>135325621</v>
       </c>
       <c r="B34" t="n">
         <v>91970</v>
@@ -4251,17 +4251,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>621435</v>
+        <v>621385</v>
       </c>
       <c r="R34" t="n">
-        <v>7322135</v>
+        <v>7321984</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4300,12 +4300,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Stående död gran</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4320,12 +4315,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4336,10 +4331,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135323539</v>
+        <v>135326368</v>
       </c>
       <c r="B35" t="n">
-        <v>91974</v>
+        <v>91970</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4347,34 +4342,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>621368</v>
+        <v>621346</v>
       </c>
       <c r="R35" t="n">
-        <v>7322169</v>
+        <v>7322011</v>
       </c>
       <c r="S35" t="n">
         <v>7</v>
@@ -4406,7 +4401,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4416,7 +4411,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4431,22 +4426,26 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135325617</v>
+        <v>135329807</v>
       </c>
       <c r="B36" t="n">
-        <v>91974</v>
+        <v>91970</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4454,34 +4453,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>621477</v>
+        <v>621435</v>
       </c>
       <c r="R36" t="n">
-        <v>7322015</v>
+        <v>7322135</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4513,7 +4512,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4523,7 +4522,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Stående död gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4538,12 +4542,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4554,7 +4558,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135325631</v>
+        <v>135323539</v>
       </c>
       <c r="B37" t="n">
         <v>91974</v>
@@ -4585,17 +4589,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>621324</v>
+        <v>621368</v>
       </c>
       <c r="R37" t="n">
-        <v>7322178</v>
+        <v>7322169</v>
       </c>
       <c r="S37" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4624,7 +4628,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4634,7 +4638,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4649,23 +4653,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135326370</v>
+        <v>135325617</v>
       </c>
       <c r="B38" t="n">
         <v>91974</v>
@@ -4696,17 +4696,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>621362</v>
+        <v>621477</v>
       </c>
       <c r="R38" t="n">
         <v>7322015</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,12 +4760,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4776,7 +4776,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135326374</v>
+        <v>135325631</v>
       </c>
       <c r="B39" t="n">
         <v>91974</v>
@@ -4807,17 +4807,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>621407</v>
+        <v>621324</v>
       </c>
       <c r="R39" t="n">
-        <v>7322006</v>
+        <v>7322178</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4871,12 +4871,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4887,7 +4887,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135326488</v>
+        <v>135326370</v>
       </c>
       <c r="B40" t="n">
         <v>91974</v>
@@ -4918,17 +4918,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>621223</v>
+        <v>621362</v>
       </c>
       <c r="R40" t="n">
-        <v>7322025</v>
+        <v>7322015</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4982,12 +4982,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4998,7 +4998,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135326491</v>
+        <v>135326374</v>
       </c>
       <c r="B41" t="n">
         <v>91974</v>
@@ -5029,17 +5029,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>621281</v>
+        <v>621407</v>
       </c>
       <c r="R41" t="n">
-        <v>7322013</v>
+        <v>7322006</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5093,12 +5093,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5109,7 +5109,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135326493</v>
+        <v>135326488</v>
       </c>
       <c r="B42" t="n">
         <v>91974</v>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>621282</v>
+        <v>621223</v>
       </c>
       <c r="R42" t="n">
-        <v>7321987</v>
+        <v>7322025</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5220,7 +5220,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135326528</v>
+        <v>135326491</v>
       </c>
       <c r="B43" t="n">
         <v>91974</v>
@@ -5251,17 +5251,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>621179</v>
+        <v>621281</v>
       </c>
       <c r="R43" t="n">
-        <v>7321981</v>
+        <v>7322013</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5315,12 +5315,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5331,7 +5331,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135330949</v>
+        <v>135326493</v>
       </c>
       <c r="B44" t="n">
         <v>91974</v>
@@ -5362,17 +5362,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>621255</v>
+        <v>621282</v>
       </c>
       <c r="R44" t="n">
-        <v>7322247</v>
+        <v>7321987</v>
       </c>
       <c r="S44" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5426,12 +5426,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5442,7 +5442,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135330959</v>
+        <v>135326528</v>
       </c>
       <c r="B45" t="n">
         <v>91974</v>
@@ -5473,17 +5473,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>621325</v>
+        <v>621179</v>
       </c>
       <c r="R45" t="n">
-        <v>7322254</v>
+        <v>7321981</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5537,12 +5537,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5553,48 +5553,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135329809</v>
+        <v>135330949</v>
       </c>
       <c r="B46" t="n">
-        <v>91988</v>
+        <v>91974</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>621360</v>
+        <v>621255</v>
       </c>
       <c r="R46" t="n">
-        <v>7322150</v>
+        <v>7322247</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5633,12 +5633,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Låga</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5653,12 +5648,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5669,32 +5664,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135330960</v>
+        <v>135330959</v>
       </c>
       <c r="B47" t="n">
-        <v>91988</v>
+        <v>91974</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5704,13 +5699,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>621326</v>
+        <v>621325</v>
       </c>
       <c r="R47" t="n">
-        <v>7322247</v>
+        <v>7322254</v>
       </c>
       <c r="S47" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5739,7 +5734,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5749,7 +5744,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5780,7 +5775,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135330963</v>
+        <v>135329809</v>
       </c>
       <c r="B48" t="n">
         <v>91988</v>
@@ -5811,14 +5806,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>621313</v>
+        <v>621360</v>
       </c>
       <c r="R48" t="n">
-        <v>7322173</v>
+        <v>7322150</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5850,7 +5845,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5860,7 +5855,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Låga</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5875,12 +5875,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5891,48 +5891,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135323148</v>
+        <v>135330960</v>
       </c>
       <c r="B49" t="n">
-        <v>83222</v>
+        <v>91988</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>621493</v>
+        <v>621326</v>
       </c>
       <c r="R49" t="n">
-        <v>7322104</v>
+        <v>7322247</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5986,12 +5986,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6002,45 +6002,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135323159</v>
+        <v>135330963</v>
       </c>
       <c r="B50" t="n">
-        <v>83222</v>
+        <v>91988</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>621497</v>
+        <v>621313</v>
       </c>
       <c r="R50" t="n">
-        <v>7322062</v>
+        <v>7322173</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6097,12 +6097,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6113,7 +6113,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135325599</v>
+        <v>135323148</v>
       </c>
       <c r="B51" t="n">
         <v>83222</v>
@@ -6144,17 +6144,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
         <v>621493</v>
       </c>
       <c r="R51" t="n">
-        <v>7322087</v>
+        <v>7322104</v>
       </c>
       <c r="S51" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6208,12 +6208,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6224,7 +6224,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135325625</v>
+        <v>135323159</v>
       </c>
       <c r="B52" t="n">
         <v>83222</v>
@@ -6255,14 +6255,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>621351</v>
+        <v>621497</v>
       </c>
       <c r="R52" t="n">
-        <v>7322003</v>
+        <v>7322062</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6319,12 +6319,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6335,7 +6335,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135326511</v>
+        <v>135325599</v>
       </c>
       <c r="B53" t="n">
         <v>83222</v>
@@ -6366,17 +6366,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>621157</v>
+        <v>621493</v>
       </c>
       <c r="R53" t="n">
-        <v>7322072</v>
+        <v>7322087</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6430,12 +6430,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6446,7 +6446,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135326520</v>
+        <v>135325625</v>
       </c>
       <c r="B54" t="n">
         <v>83222</v>
@@ -6477,17 +6477,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>621266</v>
+        <v>621351</v>
       </c>
       <c r="R54" t="n">
-        <v>7322031</v>
+        <v>7322003</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6541,12 +6541,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6557,7 +6557,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135329841</v>
+        <v>135326511</v>
       </c>
       <c r="B55" t="n">
         <v>83222</v>
@@ -6588,14 +6588,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>621163</v>
+        <v>621157</v>
       </c>
       <c r="R55" t="n">
-        <v>7322058</v>
+        <v>7322072</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6652,12 +6652,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6668,48 +6668,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135326367</v>
+        <v>135326520</v>
       </c>
       <c r="B56" t="n">
-        <v>92329</v>
+        <v>83222</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>621316</v>
+        <v>621266</v>
       </c>
       <c r="R56" t="n">
-        <v>7322007</v>
+        <v>7322031</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6763,12 +6763,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6779,48 +6779,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135326373</v>
+        <v>135329841</v>
       </c>
       <c r="B57" t="n">
-        <v>92329</v>
+        <v>83222</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>621407</v>
+        <v>621163</v>
       </c>
       <c r="R57" t="n">
-        <v>7322006</v>
+        <v>7322058</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6874,12 +6874,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6890,7 +6890,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135326376</v>
+        <v>135326367</v>
       </c>
       <c r="B58" t="n">
         <v>92329</v>
@@ -6925,13 +6925,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>621413</v>
+        <v>621316</v>
       </c>
       <c r="R58" t="n">
-        <v>7322044</v>
+        <v>7322007</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7001,48 +7001,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135323164</v>
+        <v>135326373</v>
       </c>
       <c r="B59" t="n">
-        <v>92167</v>
+        <v>92329</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1588</v>
+        <v>1506</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>621465</v>
+        <v>621407</v>
       </c>
       <c r="R59" t="n">
-        <v>7322032</v>
+        <v>7322006</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7096,12 +7096,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7112,10 +7112,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135323540</v>
+        <v>135326376</v>
       </c>
       <c r="B60" t="n">
-        <v>92318</v>
+        <v>92329</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7123,37 +7123,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2062</v>
+        <v>1506</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>621368</v>
+        <v>621413</v>
       </c>
       <c r="R60" t="n">
-        <v>7322169</v>
+        <v>7322044</v>
       </c>
       <c r="S60" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7207,60 +7207,64 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135330951</v>
+        <v>135323164</v>
       </c>
       <c r="B61" t="n">
-        <v>92318</v>
+        <v>92167</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2062</v>
+        <v>1588</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>621257</v>
+        <v>621465</v>
       </c>
       <c r="R61" t="n">
-        <v>7322248</v>
+        <v>7322032</v>
       </c>
       <c r="S61" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7289,7 +7293,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7299,7 +7303,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7314,12 +7318,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7330,48 +7334,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135323167</v>
+        <v>135323540</v>
       </c>
       <c r="B62" t="n">
-        <v>91937</v>
+        <v>92318</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>621418</v>
+        <v>621368</v>
       </c>
       <c r="R62" t="n">
-        <v>7321963</v>
+        <v>7322169</v>
       </c>
       <c r="S62" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7400,7 +7404,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7410,7 +7414,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7425,64 +7429,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135323542</v>
+        <v>135330951</v>
       </c>
       <c r="B63" t="n">
-        <v>91937</v>
+        <v>92318</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>621359</v>
+        <v>621257</v>
       </c>
       <c r="R63" t="n">
-        <v>7322116</v>
+        <v>7322248</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7536,44 +7536,48 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135323149</v>
+        <v>135323167</v>
       </c>
       <c r="B64" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7583,13 +7587,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>621499</v>
+        <v>621418</v>
       </c>
       <c r="R64" t="n">
-        <v>7322092</v>
+        <v>7321963</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7618,7 +7622,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7628,7 +7632,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7659,48 +7663,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135323173</v>
+        <v>135323542</v>
       </c>
       <c r="B65" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>621355</v>
+        <v>621359</v>
       </c>
       <c r="R65" t="n">
-        <v>7321983</v>
+        <v>7322116</v>
       </c>
       <c r="S65" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7729,7 +7733,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7739,7 +7743,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7754,23 +7758,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135325598</v>
+        <v>135323149</v>
       </c>
       <c r="B66" t="n">
         <v>79373</v>
@@ -7801,17 +7801,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>621493</v>
+        <v>621499</v>
       </c>
       <c r="R66" t="n">
-        <v>7322096</v>
+        <v>7322092</v>
       </c>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7865,12 +7865,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7881,7 +7881,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135325620</v>
+        <v>135323173</v>
       </c>
       <c r="B67" t="n">
         <v>79373</v>
@@ -7912,17 +7912,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>621429</v>
+        <v>621355</v>
       </c>
       <c r="R67" t="n">
-        <v>7321989</v>
+        <v>7321983</v>
       </c>
       <c r="S67" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7976,12 +7976,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7992,7 +7992,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135325622</v>
+        <v>135325598</v>
       </c>
       <c r="B68" t="n">
         <v>79373</v>
@@ -8027,13 +8027,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>621392</v>
+        <v>621493</v>
       </c>
       <c r="R68" t="n">
-        <v>7321985</v>
+        <v>7322096</v>
       </c>
       <c r="S68" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8103,7 +8103,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135326492</v>
+        <v>135325620</v>
       </c>
       <c r="B69" t="n">
         <v>79373</v>
@@ -8134,17 +8134,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>621275</v>
+        <v>621429</v>
       </c>
       <c r="R69" t="n">
-        <v>7322022</v>
+        <v>7321989</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8198,12 +8198,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8214,7 +8214,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135326518</v>
+        <v>135325622</v>
       </c>
       <c r="B70" t="n">
         <v>79373</v>
@@ -8245,17 +8245,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>621266</v>
+        <v>621392</v>
       </c>
       <c r="R70" t="n">
-        <v>7322033</v>
+        <v>7321985</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8309,12 +8309,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8325,7 +8325,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135329852</v>
+        <v>135326492</v>
       </c>
       <c r="B71" t="n">
         <v>79373</v>
@@ -8356,17 +8356,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>621266</v>
+        <v>621275</v>
       </c>
       <c r="R71" t="n">
-        <v>7322030</v>
+        <v>7322022</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8420,12 +8420,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8436,7 +8436,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135329854</v>
+        <v>135326518</v>
       </c>
       <c r="B72" t="n">
         <v>79373</v>
@@ -8467,14 +8467,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>621314</v>
+        <v>621266</v>
       </c>
       <c r="R72" t="n">
-        <v>7322003</v>
+        <v>7322033</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8531,12 +8531,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8547,48 +8547,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135326484</v>
+        <v>135329852</v>
       </c>
       <c r="B73" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>621167</v>
+        <v>621266</v>
       </c>
       <c r="R73" t="n">
-        <v>7322046</v>
+        <v>7322030</v>
       </c>
       <c r="S73" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8642,12 +8642,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8658,48 +8658,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135323162</v>
+        <v>135329854</v>
       </c>
       <c r="B74" t="n">
-        <v>83341</v>
+        <v>79373</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>621495</v>
+        <v>621314</v>
       </c>
       <c r="R74" t="n">
-        <v>7322022</v>
+        <v>7322003</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8753,12 +8753,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8769,10 +8769,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135323147</v>
+        <v>135326484</v>
       </c>
       <c r="B75" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,37 +8780,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>621480</v>
+        <v>621167</v>
       </c>
       <c r="R75" t="n">
-        <v>7322096</v>
+        <v>7322046</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8864,12 +8864,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8880,32 +8880,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135323151</v>
+        <v>135323162</v>
       </c>
       <c r="B76" t="n">
-        <v>83358</v>
+        <v>83341</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8915,13 +8915,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>621502</v>
+        <v>621495</v>
       </c>
       <c r="R76" t="n">
-        <v>7322088</v>
+        <v>7322022</v>
       </c>
       <c r="S76" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8991,7 +8991,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135325600</v>
+        <v>135323147</v>
       </c>
       <c r="B77" t="n">
         <v>83358</v>
@@ -9022,17 +9022,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>621487</v>
+        <v>621480</v>
       </c>
       <c r="R77" t="n">
-        <v>7322053</v>
+        <v>7322096</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9086,12 +9086,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9102,7 +9102,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135325618</v>
+        <v>135323151</v>
       </c>
       <c r="B78" t="n">
         <v>83358</v>
@@ -9133,17 +9133,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>621472</v>
+        <v>621502</v>
       </c>
       <c r="R78" t="n">
-        <v>7322001</v>
+        <v>7322088</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9197,12 +9197,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9213,7 +9213,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135325624</v>
+        <v>135325600</v>
       </c>
       <c r="B79" t="n">
         <v>83358</v>
@@ -9248,13 +9248,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>621351</v>
+        <v>621487</v>
       </c>
       <c r="R79" t="n">
-        <v>7322003</v>
+        <v>7322053</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9324,7 +9324,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135326486</v>
+        <v>135325618</v>
       </c>
       <c r="B80" t="n">
         <v>83358</v>
@@ -9355,17 +9355,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>621203</v>
+        <v>621472</v>
       </c>
       <c r="R80" t="n">
-        <v>7322017</v>
+        <v>7322001</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9419,12 +9419,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9435,7 +9435,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135326495</v>
+        <v>135325624</v>
       </c>
       <c r="B81" t="n">
         <v>83358</v>
@@ -9466,14 +9466,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>621271</v>
+        <v>621351</v>
       </c>
       <c r="R81" t="n">
-        <v>7321971</v>
+        <v>7322003</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9530,12 +9530,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9546,7 +9546,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135326523</v>
+        <v>135326486</v>
       </c>
       <c r="B82" t="n">
         <v>83358</v>
@@ -9577,14 +9577,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>621284</v>
+        <v>621203</v>
       </c>
       <c r="R82" t="n">
-        <v>7322012</v>
+        <v>7322017</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9616,7 +9616,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9641,12 +9641,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9657,7 +9657,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135329844</v>
+        <v>135326495</v>
       </c>
       <c r="B83" t="n">
         <v>83358</v>
@@ -9688,17 +9688,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>621207</v>
+        <v>621271</v>
       </c>
       <c r="R83" t="n">
-        <v>7322034</v>
+        <v>7321971</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9752,12 +9752,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9768,10 +9768,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135322206</v>
+        <v>135326523</v>
       </c>
       <c r="B84" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9779,37 +9779,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>621158</v>
+        <v>621284</v>
       </c>
       <c r="R84" t="n">
-        <v>7322094</v>
+        <v>7322012</v>
       </c>
       <c r="S84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9863,12 +9863,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9879,10 +9879,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135323169</v>
+        <v>135329844</v>
       </c>
       <c r="B85" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9890,37 +9890,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>621411</v>
+        <v>621207</v>
       </c>
       <c r="R85" t="n">
-        <v>7321964</v>
+        <v>7322034</v>
       </c>
       <c r="S85" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9974,12 +9974,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9990,7 +9990,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135325627</v>
+        <v>135322206</v>
       </c>
       <c r="B86" t="n">
         <v>79992</v>
@@ -10021,17 +10021,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>621323</v>
+        <v>621158</v>
       </c>
       <c r="R86" t="n">
-        <v>7321957</v>
+        <v>7322094</v>
       </c>
       <c r="S86" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10085,12 +10085,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10101,7 +10101,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135325629</v>
+        <v>135323169</v>
       </c>
       <c r="B87" t="n">
         <v>79992</v>
@@ -10132,17 +10132,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>621316</v>
+        <v>621411</v>
       </c>
       <c r="R87" t="n">
-        <v>7322179</v>
+        <v>7321964</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10196,12 +10196,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10212,7 +10212,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135329808</v>
+        <v>135325627</v>
       </c>
       <c r="B88" t="n">
         <v>79992</v>
@@ -10243,17 +10243,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>621315</v>
+        <v>621323</v>
       </c>
       <c r="R88" t="n">
-        <v>7322181</v>
+        <v>7321957</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10292,12 +10292,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10312,12 +10307,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10328,7 +10323,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135330953</v>
+        <v>135325629</v>
       </c>
       <c r="B89" t="n">
         <v>79992</v>
@@ -10359,17 +10354,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>621277</v>
+        <v>621316</v>
       </c>
       <c r="R89" t="n">
-        <v>7322238</v>
+        <v>7322179</v>
       </c>
       <c r="S89" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10398,7 +10393,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10408,7 +10403,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10423,12 +10418,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10439,10 +10434,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135325633</v>
+        <v>135329808</v>
       </c>
       <c r="B90" t="n">
-        <v>78377</v>
+        <v>79992</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10450,37 +10445,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>621287</v>
+        <v>621315</v>
       </c>
       <c r="R90" t="n">
-        <v>7322205</v>
+        <v>7322181</v>
       </c>
       <c r="S90" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10509,7 +10504,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10519,7 +10514,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10534,12 +10534,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10550,10 +10550,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135330943</v>
+        <v>135330953</v>
       </c>
       <c r="B91" t="n">
-        <v>78377</v>
+        <v>79992</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10561,21 +10561,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10585,13 +10585,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>621177</v>
+        <v>621277</v>
       </c>
       <c r="R91" t="n">
-        <v>7322135</v>
+        <v>7322238</v>
       </c>
       <c r="S91" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10630,7 +10630,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10661,7 +10661,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135330946</v>
+        <v>135325633</v>
       </c>
       <c r="B92" t="n">
         <v>78377</v>
@@ -10692,17 +10692,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>621194</v>
+        <v>621287</v>
       </c>
       <c r="R92" t="n">
-        <v>7322206</v>
+        <v>7322205</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10756,12 +10756,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10772,10 +10772,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135323175</v>
+        <v>135330943</v>
       </c>
       <c r="B93" t="n">
-        <v>57975</v>
+        <v>78377</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10783,42 +10783,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>621152</v>
+        <v>621177</v>
       </c>
       <c r="R93" t="n">
-        <v>7321996</v>
+        <v>7322135</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10847,7 +10842,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10857,7 +10852,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10872,12 +10867,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10888,10 +10883,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135323536</v>
+        <v>135330946</v>
       </c>
       <c r="B94" t="n">
-        <v>57975</v>
+        <v>78377</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10899,34 +10894,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>621461</v>
+        <v>621194</v>
       </c>
       <c r="R94" t="n">
-        <v>7322142</v>
+        <v>7322206</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10958,7 +10953,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10968,12 +10963,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10988,19 +10978,23 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135326366</v>
+        <v>135323175</v>
       </c>
       <c r="B95" t="n">
         <v>57975</v>
@@ -11029,27 +11023,24 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>621323</v>
+        <v>621152</v>
       </c>
       <c r="R95" t="n">
-        <v>7322015</v>
+        <v>7321996</v>
       </c>
       <c r="S95" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11078,7 +11069,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11088,12 +11079,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11108,12 +11094,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11124,7 +11110,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135326496</v>
+        <v>135323536</v>
       </c>
       <c r="B96" t="n">
         <v>57975</v>
@@ -11153,27 +11139,19 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>621246</v>
+        <v>621461</v>
       </c>
       <c r="R96" t="n">
-        <v>7321956</v>
+        <v>7322142</v>
       </c>
       <c r="S96" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11202,7 +11180,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11212,12 +11190,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11232,23 +11210,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135326497</v>
+        <v>135326366</v>
       </c>
       <c r="B97" t="n">
         <v>57975</v>
@@ -11287,17 +11261,17 @@
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>621165</v>
+        <v>621323</v>
       </c>
       <c r="R97" t="n">
-        <v>7322002</v>
+        <v>7322015</v>
       </c>
       <c r="S97" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11326,7 +11300,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11336,12 +11310,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11356,12 +11330,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11372,7 +11346,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135329838</v>
+        <v>135326496</v>
       </c>
       <c r="B98" t="n">
         <v>57975</v>
@@ -11401,19 +11375,27 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>621123</v>
+        <v>621246</v>
       </c>
       <c r="R98" t="n">
-        <v>7322113</v>
+        <v>7321956</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11442,7 +11424,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11452,12 +11434,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11472,12 +11454,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11488,7 +11470,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135329861</v>
+        <v>135326497</v>
       </c>
       <c r="B99" t="n">
         <v>57975</v>
@@ -11517,19 +11499,27 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>621226</v>
+        <v>621165</v>
       </c>
       <c r="R99" t="n">
-        <v>7322073</v>
+        <v>7322002</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11558,7 +11548,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11568,12 +11558,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11588,12 +11578,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11604,7 +11594,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135330957</v>
+        <v>135329838</v>
       </c>
       <c r="B100" t="n">
         <v>57975</v>
@@ -11633,24 +11623,19 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>621320</v>
+        <v>621123</v>
       </c>
       <c r="R100" t="n">
-        <v>7322249</v>
+        <v>7322113</v>
       </c>
       <c r="S100" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11679,7 +11664,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11689,12 +11674,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11709,12 +11694,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11725,7 +11710,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135330964</v>
+        <v>135329861</v>
       </c>
       <c r="B101" t="n">
         <v>57975</v>
@@ -11754,27 +11739,19 @@
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>621397</v>
+        <v>621226</v>
       </c>
       <c r="R101" t="n">
-        <v>7322108</v>
+        <v>7322073</v>
       </c>
       <c r="S101" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11803,7 +11780,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11813,12 +11790,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11833,12 +11810,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11849,7 +11826,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135330965</v>
+        <v>135330957</v>
       </c>
       <c r="B102" t="n">
         <v>57975</v>
@@ -11878,27 +11855,24 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>621436</v>
+        <v>621320</v>
       </c>
       <c r="R102" t="n">
-        <v>7322109</v>
+        <v>7322249</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11927,7 +11901,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11937,12 +11911,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11973,7 +11947,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135330966</v>
+        <v>135330964</v>
       </c>
       <c r="B103" t="n">
         <v>57975</v>
@@ -12006,7 +11980,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -12016,13 +11990,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>621459</v>
+        <v>621397</v>
       </c>
       <c r="R103" t="n">
-        <v>7322135</v>
+        <v>7322108</v>
       </c>
       <c r="S103" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12051,7 +12025,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12061,12 +12035,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12097,7 +12071,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135330967</v>
+        <v>135330965</v>
       </c>
       <c r="B104" t="n">
         <v>57975</v>
@@ -12140,13 +12114,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>621219</v>
+        <v>621436</v>
       </c>
       <c r="R104" t="n">
-        <v>7322131</v>
+        <v>7322109</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12175,7 +12149,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12185,12 +12159,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Spår av födosök</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12221,44 +12195,40 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135330945</v>
+        <v>135330966</v>
       </c>
       <c r="B105" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -12268,13 +12238,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>621163</v>
+        <v>621459</v>
       </c>
       <c r="R105" t="n">
-        <v>7322161</v>
+        <v>7322135</v>
       </c>
       <c r="S105" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12303,7 +12273,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12313,12 +12283,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Uppflygande</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12349,10 +12319,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135326371</v>
+        <v>135330967</v>
       </c>
       <c r="B106" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12360,37 +12330,45 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>621395</v>
+        <v>621219</v>
       </c>
       <c r="R106" t="n">
-        <v>7322009</v>
+        <v>7322131</v>
       </c>
       <c r="S106" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12419,7 +12397,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12429,7 +12407,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Spår av födosök</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12444,12 +12427,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -12460,32 +12443,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135326513</v>
+        <v>135330945</v>
       </c>
       <c r="B107" t="n">
-        <v>41606</v>
+        <v>57162</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>215713</v>
+        <v>100138</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -12493,19 +12476,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>621171</v>
+        <v>621163</v>
       </c>
       <c r="R107" t="n">
-        <v>7322040</v>
+        <v>7322161</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12534,7 +12525,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12544,7 +12535,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12559,12 +12555,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -12575,48 +12571,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135326512</v>
+        <v>135326371</v>
       </c>
       <c r="B108" t="n">
-        <v>98066</v>
+        <v>58136</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>621161</v>
+        <v>621395</v>
       </c>
       <c r="R108" t="n">
-        <v>7322070</v>
+        <v>7322009</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12645,7 +12641,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12655,7 +12651,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12670,12 +12666,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12686,10 +12682,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135326487</v>
+        <v>135326513</v>
       </c>
       <c r="B109" t="n">
-        <v>78382</v>
+        <v>41606</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12697,37 +12693,41 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228579</v>
+        <v>215713</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>621204</v>
+        <v>621171</v>
       </c>
       <c r="R109" t="n">
-        <v>7322016</v>
+        <v>7322040</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12781,12 +12781,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -12797,32 +12797,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135326521</v>
+        <v>135326512</v>
       </c>
       <c r="B110" t="n">
-        <v>78382</v>
+        <v>98066</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228579</v>
+        <v>221941</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12832,10 +12832,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>621266</v>
+        <v>621161</v>
       </c>
       <c r="R110" t="n">
-        <v>7322030</v>
+        <v>7322070</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12908,7 +12908,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135326526</v>
+        <v>135326487</v>
       </c>
       <c r="B111" t="n">
         <v>78382</v>
@@ -12939,17 +12939,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>621284</v>
+        <v>621204</v>
       </c>
       <c r="R111" t="n">
-        <v>7322006</v>
+        <v>7322016</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13003,12 +13003,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -13019,10 +13019,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135326483</v>
+        <v>135326521</v>
       </c>
       <c r="B112" t="n">
-        <v>79396</v>
+        <v>78382</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13030,37 +13030,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>260591</v>
+        <v>228579</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>621165</v>
+        <v>621266</v>
       </c>
       <c r="R112" t="n">
-        <v>7322074</v>
+        <v>7322030</v>
       </c>
       <c r="S112" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13099,7 +13099,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13114,12 +13114,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -13130,10 +13130,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135325606</v>
+        <v>135326526</v>
       </c>
       <c r="B113" t="n">
-        <v>92245</v>
+        <v>78382</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13141,37 +13141,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>658</v>
+        <v>228579</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>621546</v>
+        <v>621284</v>
       </c>
       <c r="R113" t="n">
-        <v>7322049</v>
+        <v>7322006</v>
       </c>
       <c r="S113" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13210,7 +13210,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13225,12 +13225,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -13241,10 +13241,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135323160</v>
+        <v>135326483</v>
       </c>
       <c r="B114" t="n">
-        <v>79452</v>
+        <v>79396</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13252,37 +13252,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>864</v>
+        <v>260591</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>621529</v>
+        <v>621165</v>
       </c>
       <c r="R114" t="n">
-        <v>7322033</v>
+        <v>7322074</v>
       </c>
       <c r="S114" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13336,12 +13336,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -13352,48 +13352,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135323154</v>
+        <v>135325606</v>
       </c>
       <c r="B115" t="n">
-        <v>92795</v>
+        <v>92245</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>918</v>
+        <v>658</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>621513</v>
+        <v>621546</v>
       </c>
       <c r="R115" t="n">
-        <v>7322084</v>
+        <v>7322049</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13432,7 +13432,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13447,12 +13447,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -13463,32 +13463,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135323161</v>
+        <v>135323160</v>
       </c>
       <c r="B116" t="n">
-        <v>92795</v>
+        <v>79452</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>918</v>
+        <v>864</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13498,13 +13498,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>621535</v>
+        <v>621529</v>
       </c>
       <c r="R116" t="n">
         <v>7322033</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13543,7 +13543,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13574,7 +13574,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135325607</v>
+        <v>135323154</v>
       </c>
       <c r="B117" t="n">
         <v>92795</v>
@@ -13605,14 +13605,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>621551</v>
+        <v>621513</v>
       </c>
       <c r="R117" t="n">
-        <v>7322047</v>
+        <v>7322084</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13644,7 +13644,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13669,12 +13669,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -13685,7 +13685,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135325611</v>
+        <v>135323161</v>
       </c>
       <c r="B118" t="n">
         <v>92795</v>
@@ -13716,17 +13716,17 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>621536</v>
+        <v>621535</v>
       </c>
       <c r="R118" t="n">
-        <v>7322045</v>
+        <v>7322033</v>
       </c>
       <c r="S118" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13780,12 +13780,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -13796,32 +13796,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135325610</v>
+        <v>135325607</v>
       </c>
       <c r="B119" t="n">
-        <v>91970</v>
+        <v>92795</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13831,13 +13831,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>621539</v>
+        <v>621551</v>
       </c>
       <c r="R119" t="n">
-        <v>7322038</v>
+        <v>7322047</v>
       </c>
       <c r="S119" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13876,7 +13876,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13907,32 +13907,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135325608</v>
+        <v>135325611</v>
       </c>
       <c r="B120" t="n">
-        <v>91974</v>
+        <v>92795</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>918</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13942,13 +13942,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>621550</v>
+        <v>621536</v>
       </c>
       <c r="R120" t="n">
-        <v>7322047</v>
+        <v>7322045</v>
       </c>
       <c r="S120" t="n">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14018,10 +14018,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135325601</v>
+        <v>135325610</v>
       </c>
       <c r="B121" t="n">
-        <v>83222</v>
+        <v>91970</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14029,21 +14029,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14053,13 +14053,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>621522</v>
+        <v>621539</v>
       </c>
       <c r="R121" t="n">
-        <v>7322095</v>
+        <v>7322038</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14098,12 +14098,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Cinnoberflamlav</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14134,10 +14129,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135325603</v>
+        <v>135325608</v>
       </c>
       <c r="B122" t="n">
-        <v>83222</v>
+        <v>91974</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14145,21 +14140,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14169,13 +14164,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>621524</v>
+        <v>621550</v>
       </c>
       <c r="R122" t="n">
-        <v>7322055</v>
+        <v>7322047</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14204,7 +14199,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14214,7 +14209,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14245,48 +14240,48 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135323155</v>
+        <v>135325601</v>
       </c>
       <c r="B123" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>621518</v>
+        <v>621522</v>
       </c>
       <c r="R123" t="n">
-        <v>7322064</v>
+        <v>7322095</v>
       </c>
       <c r="S123" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14315,7 +14310,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14325,7 +14320,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Cinnoberflamlav</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14340,12 +14340,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -14356,10 +14356,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135325602</v>
+        <v>135325603</v>
       </c>
       <c r="B124" t="n">
-        <v>83358</v>
+        <v>83222</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14367,21 +14367,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14391,13 +14391,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>621515</v>
+        <v>621524</v>
       </c>
       <c r="R124" t="n">
-        <v>7322081</v>
+        <v>7322055</v>
       </c>
       <c r="S124" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14467,48 +14467,48 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135325609</v>
+        <v>135323155</v>
       </c>
       <c r="B125" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>621545</v>
+        <v>621518</v>
       </c>
       <c r="R125" t="n">
-        <v>7322048</v>
+        <v>7322064</v>
       </c>
       <c r="S125" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14562,12 +14562,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -14578,48 +14578,48 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135323153</v>
+        <v>135325602</v>
       </c>
       <c r="B126" t="n">
-        <v>78731</v>
+        <v>83358</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6443</v>
+        <v>6440</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>621513</v>
+        <v>621515</v>
       </c>
       <c r="R126" t="n">
-        <v>7322084</v>
+        <v>7322081</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14658,12 +14658,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>På torr grangren</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14678,15 +14673,242 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>135325609</v>
+      </c>
+      <c r="B127" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>621545</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7322048</v>
+      </c>
+      <c r="S127" t="n">
+        <v>26</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>135323153</v>
+      </c>
+      <c r="B128" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Sotlav</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Acolium inquinans</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Skornjamyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>621513</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7322084</v>
+      </c>
+      <c r="S128" t="n">
+        <v>5</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>På torr grangren</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
           <t>Cajsa Björkén</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
+      <c r="AX128" t="inlineStr">
         <is>
           <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
-      <c r="AY126" t="inlineStr">
+      <c r="AY128" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -1042,6 +1042,9 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Maskaure Skornjamyran / Renskötartjärnen, Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
@@ -1102,6 +1105,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1116,7 +1120,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">

--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY128"/>
+  <dimension ref="A1:AY129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7560,10 +7560,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135323167</v>
+        <v>135323941</v>
       </c>
       <c r="B64" t="n">
-        <v>91937</v>
+        <v>96678</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7571,37 +7571,41 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>2166</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>621418</v>
+        <v>621202</v>
       </c>
       <c r="R64" t="n">
-        <v>7321963</v>
+        <v>7322052</v>
       </c>
       <c r="S64" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7630,7 +7634,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7640,7 +7644,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7649,18 +7653,34 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Grov kraftig nedbruten tallåga # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7671,7 +7691,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135323542</v>
+        <v>135323167</v>
       </c>
       <c r="B65" t="n">
         <v>91937</v>
@@ -7702,17 +7722,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>621359</v>
+        <v>621418</v>
       </c>
       <c r="R65" t="n">
-        <v>7322116</v>
+        <v>7321963</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7741,7 +7761,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7751,7 +7771,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7766,60 +7786,64 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135323149</v>
+        <v>135323542</v>
       </c>
       <c r="B66" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>621499</v>
+        <v>621359</v>
       </c>
       <c r="R66" t="n">
-        <v>7322092</v>
+        <v>7322116</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7848,7 +7872,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7858,7 +7882,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7873,23 +7897,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135323173</v>
+        <v>135323149</v>
       </c>
       <c r="B67" t="n">
         <v>79373</v>
@@ -7924,13 +7944,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>621355</v>
+        <v>621499</v>
       </c>
       <c r="R67" t="n">
-        <v>7321983</v>
+        <v>7322092</v>
       </c>
       <c r="S67" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7959,7 +7979,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7969,7 +7989,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8000,7 +8020,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135325598</v>
+        <v>135323173</v>
       </c>
       <c r="B68" t="n">
         <v>79373</v>
@@ -8031,17 +8051,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>621493</v>
+        <v>621355</v>
       </c>
       <c r="R68" t="n">
-        <v>7322096</v>
+        <v>7321983</v>
       </c>
       <c r="S68" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8070,7 +8090,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8080,7 +8100,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8095,12 +8115,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8111,7 +8131,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135325620</v>
+        <v>135325598</v>
       </c>
       <c r="B69" t="n">
         <v>79373</v>
@@ -8146,13 +8166,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>621429</v>
+        <v>621493</v>
       </c>
       <c r="R69" t="n">
-        <v>7321989</v>
+        <v>7322096</v>
       </c>
       <c r="S69" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8181,7 +8201,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8191,7 +8211,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8222,7 +8242,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135325622</v>
+        <v>135325620</v>
       </c>
       <c r="B70" t="n">
         <v>79373</v>
@@ -8257,10 +8277,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>621392</v>
+        <v>621429</v>
       </c>
       <c r="R70" t="n">
-        <v>7321985</v>
+        <v>7321989</v>
       </c>
       <c r="S70" t="n">
         <v>26</v>
@@ -8292,7 +8312,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8302,7 +8322,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8333,7 +8353,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135326492</v>
+        <v>135325622</v>
       </c>
       <c r="B71" t="n">
         <v>79373</v>
@@ -8364,17 +8384,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>621275</v>
+        <v>621392</v>
       </c>
       <c r="R71" t="n">
-        <v>7322022</v>
+        <v>7321985</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8403,7 +8423,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8413,7 +8433,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8428,12 +8448,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8444,7 +8464,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135326518</v>
+        <v>135326492</v>
       </c>
       <c r="B72" t="n">
         <v>79373</v>
@@ -8475,17 +8495,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>621266</v>
+        <v>621275</v>
       </c>
       <c r="R72" t="n">
-        <v>7322033</v>
+        <v>7322022</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8514,7 +8534,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8524,7 +8544,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8539,12 +8559,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8555,7 +8575,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135329852</v>
+        <v>135326518</v>
       </c>
       <c r="B73" t="n">
         <v>79373</v>
@@ -8586,14 +8606,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
         <v>621266</v>
       </c>
       <c r="R73" t="n">
-        <v>7322030</v>
+        <v>7322033</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8625,7 +8645,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8635,7 +8655,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8650,12 +8670,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8666,7 +8686,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135329854</v>
+        <v>135329852</v>
       </c>
       <c r="B74" t="n">
         <v>79373</v>
@@ -8701,10 +8721,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>621314</v>
+        <v>621266</v>
       </c>
       <c r="R74" t="n">
-        <v>7322003</v>
+        <v>7322030</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8736,7 +8756,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8746,7 +8766,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8777,48 +8797,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135326484</v>
+        <v>135329854</v>
       </c>
       <c r="B75" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>621167</v>
+        <v>621314</v>
       </c>
       <c r="R75" t="n">
-        <v>7322046</v>
+        <v>7322003</v>
       </c>
       <c r="S75" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8847,7 +8867,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8857,7 +8877,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8872,12 +8892,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8888,48 +8908,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135323162</v>
+        <v>135326484</v>
       </c>
       <c r="B76" t="n">
-        <v>83341</v>
+        <v>78776</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6439</v>
+        <v>6437</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>621495</v>
+        <v>621167</v>
       </c>
       <c r="R76" t="n">
-        <v>7322022</v>
+        <v>7322046</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8958,7 +8978,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8968,7 +8988,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8983,12 +9003,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8999,32 +9019,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135323147</v>
+        <v>135323162</v>
       </c>
       <c r="B77" t="n">
-        <v>83358</v>
+        <v>83341</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9034,13 +9054,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>621480</v>
+        <v>621495</v>
       </c>
       <c r="R77" t="n">
-        <v>7322096</v>
+        <v>7322022</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9069,7 +9089,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9079,7 +9099,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9110,7 +9130,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135323151</v>
+        <v>135323147</v>
       </c>
       <c r="B78" t="n">
         <v>83358</v>
@@ -9145,13 +9165,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>621502</v>
+        <v>621480</v>
       </c>
       <c r="R78" t="n">
-        <v>7322088</v>
+        <v>7322096</v>
       </c>
       <c r="S78" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9180,7 +9200,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9190,7 +9210,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9221,7 +9241,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135325600</v>
+        <v>135323151</v>
       </c>
       <c r="B79" t="n">
         <v>83358</v>
@@ -9252,17 +9272,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>621487</v>
+        <v>621502</v>
       </c>
       <c r="R79" t="n">
-        <v>7322053</v>
+        <v>7322088</v>
       </c>
       <c r="S79" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9316,12 +9336,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9332,7 +9352,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135325618</v>
+        <v>135325600</v>
       </c>
       <c r="B80" t="n">
         <v>83358</v>
@@ -9367,13 +9387,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>621472</v>
+        <v>621487</v>
       </c>
       <c r="R80" t="n">
-        <v>7322001</v>
+        <v>7322053</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9402,7 +9422,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9412,7 +9432,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9443,7 +9463,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135325624</v>
+        <v>135325618</v>
       </c>
       <c r="B81" t="n">
         <v>83358</v>
@@ -9478,10 +9498,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>621351</v>
+        <v>621472</v>
       </c>
       <c r="R81" t="n">
-        <v>7322003</v>
+        <v>7322001</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9513,7 +9533,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9523,7 +9543,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9554,7 +9574,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135326486</v>
+        <v>135325624</v>
       </c>
       <c r="B82" t="n">
         <v>83358</v>
@@ -9585,17 +9605,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>621203</v>
+        <v>621351</v>
       </c>
       <c r="R82" t="n">
-        <v>7322017</v>
+        <v>7322003</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9624,7 +9644,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9634,7 +9654,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9649,12 +9669,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9665,7 +9685,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135326495</v>
+        <v>135326486</v>
       </c>
       <c r="B83" t="n">
         <v>83358</v>
@@ -9700,13 +9720,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>621271</v>
+        <v>621203</v>
       </c>
       <c r="R83" t="n">
-        <v>7321971</v>
+        <v>7322017</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9735,7 +9755,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9745,7 +9765,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9776,7 +9796,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135326523</v>
+        <v>135326495</v>
       </c>
       <c r="B84" t="n">
         <v>83358</v>
@@ -9807,17 +9827,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>621284</v>
+        <v>621271</v>
       </c>
       <c r="R84" t="n">
-        <v>7322012</v>
+        <v>7321971</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9846,7 +9866,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9856,7 +9876,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9871,12 +9891,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9887,7 +9907,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135329844</v>
+        <v>135326523</v>
       </c>
       <c r="B85" t="n">
         <v>83358</v>
@@ -9918,14 +9938,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>621207</v>
+        <v>621284</v>
       </c>
       <c r="R85" t="n">
-        <v>7322034</v>
+        <v>7322012</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9957,7 +9977,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9967,7 +9987,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9982,12 +10002,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9998,10 +10018,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135322206</v>
+        <v>135329844</v>
       </c>
       <c r="B86" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10009,37 +10029,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>621158</v>
+        <v>621207</v>
       </c>
       <c r="R86" t="n">
-        <v>7322094</v>
+        <v>7322034</v>
       </c>
       <c r="S86" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10068,7 +10088,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10078,7 +10098,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10093,12 +10113,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10109,7 +10129,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135323169</v>
+        <v>135322206</v>
       </c>
       <c r="B87" t="n">
         <v>79992</v>
@@ -10140,14 +10160,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>621411</v>
+        <v>621158</v>
       </c>
       <c r="R87" t="n">
-        <v>7321964</v>
+        <v>7322094</v>
       </c>
       <c r="S87" t="n">
         <v>6</v>
@@ -10179,7 +10199,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10189,7 +10209,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10204,12 +10224,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10220,7 +10240,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135325627</v>
+        <v>135323169</v>
       </c>
       <c r="B88" t="n">
         <v>79992</v>
@@ -10251,17 +10271,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>621323</v>
+        <v>621411</v>
       </c>
       <c r="R88" t="n">
-        <v>7321957</v>
+        <v>7321964</v>
       </c>
       <c r="S88" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10290,7 +10310,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10300,7 +10320,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10315,12 +10335,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10331,7 +10351,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135325629</v>
+        <v>135325627</v>
       </c>
       <c r="B89" t="n">
         <v>79992</v>
@@ -10366,13 +10386,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>621316</v>
+        <v>621323</v>
       </c>
       <c r="R89" t="n">
-        <v>7322179</v>
+        <v>7321957</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10401,7 +10421,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10411,7 +10431,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10442,7 +10462,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135329808</v>
+        <v>135325629</v>
       </c>
       <c r="B90" t="n">
         <v>79992</v>
@@ -10473,14 +10493,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>621315</v>
+        <v>621316</v>
       </c>
       <c r="R90" t="n">
-        <v>7322181</v>
+        <v>7322179</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10512,7 +10532,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10522,12 +10542,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10542,12 +10557,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10558,7 +10573,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135330953</v>
+        <v>135329808</v>
       </c>
       <c r="B91" t="n">
         <v>79992</v>
@@ -10589,17 +10604,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>621277</v>
+        <v>621315</v>
       </c>
       <c r="R91" t="n">
-        <v>7322238</v>
+        <v>7322181</v>
       </c>
       <c r="S91" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10628,7 +10643,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10638,7 +10653,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10653,12 +10673,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10669,10 +10689,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135325633</v>
+        <v>135330953</v>
       </c>
       <c r="B92" t="n">
-        <v>78377</v>
+        <v>79992</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10680,37 +10700,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>621287</v>
+        <v>621277</v>
       </c>
       <c r="R92" t="n">
-        <v>7322205</v>
+        <v>7322238</v>
       </c>
       <c r="S92" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10739,7 +10759,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10749,7 +10769,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10764,12 +10784,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10780,7 +10800,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135330943</v>
+        <v>135325633</v>
       </c>
       <c r="B93" t="n">
         <v>78377</v>
@@ -10811,17 +10831,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>621177</v>
+        <v>621287</v>
       </c>
       <c r="R93" t="n">
-        <v>7322135</v>
+        <v>7322205</v>
       </c>
       <c r="S93" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10850,7 +10870,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10860,7 +10880,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10875,12 +10895,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10891,7 +10911,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135330946</v>
+        <v>135330943</v>
       </c>
       <c r="B94" t="n">
         <v>78377</v>
@@ -10926,13 +10946,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>621194</v>
+        <v>621177</v>
       </c>
       <c r="R94" t="n">
-        <v>7322206</v>
+        <v>7322135</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10961,7 +10981,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10971,7 +10991,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11002,10 +11022,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135323175</v>
+        <v>135330946</v>
       </c>
       <c r="B95" t="n">
-        <v>57975</v>
+        <v>78377</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11013,39 +11033,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>621152</v>
+        <v>621194</v>
       </c>
       <c r="R95" t="n">
-        <v>7321996</v>
+        <v>7322206</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11077,7 +11092,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11087,7 +11102,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11102,12 +11117,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11118,7 +11133,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135323536</v>
+        <v>135323175</v>
       </c>
       <c r="B96" t="n">
         <v>57975</v>
@@ -11147,16 +11162,21 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>621461</v>
+        <v>621152</v>
       </c>
       <c r="R96" t="n">
-        <v>7322142</v>
+        <v>7321996</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11188,7 +11208,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11198,12 +11218,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11218,19 +11233,23 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135326366</v>
+        <v>135323536</v>
       </c>
       <c r="B97" t="n">
         <v>57975</v>
@@ -11259,27 +11278,19 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>621323</v>
+        <v>621461</v>
       </c>
       <c r="R97" t="n">
-        <v>7322015</v>
+        <v>7322142</v>
       </c>
       <c r="S97" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11308,7 +11319,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11318,7 +11329,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -11338,23 +11349,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135326496</v>
+        <v>135326366</v>
       </c>
       <c r="B98" t="n">
         <v>57975</v>
@@ -11393,17 +11400,17 @@
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>621246</v>
+        <v>621323</v>
       </c>
       <c r="R98" t="n">
-        <v>7321956</v>
+        <v>7322015</v>
       </c>
       <c r="S98" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11432,7 +11439,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11442,12 +11449,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11462,12 +11469,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11478,7 +11485,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135326497</v>
+        <v>135326496</v>
       </c>
       <c r="B99" t="n">
         <v>57975</v>
@@ -11521,13 +11528,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>621165</v>
+        <v>621246</v>
       </c>
       <c r="R99" t="n">
-        <v>7322002</v>
+        <v>7321956</v>
       </c>
       <c r="S99" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11556,7 +11563,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11566,7 +11573,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -11602,7 +11609,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135329838</v>
+        <v>135326497</v>
       </c>
       <c r="B100" t="n">
         <v>57975</v>
@@ -11631,19 +11638,27 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>621123</v>
+        <v>621165</v>
       </c>
       <c r="R100" t="n">
-        <v>7322113</v>
+        <v>7322002</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11672,7 +11687,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11682,12 +11697,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11702,12 +11717,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11718,7 +11733,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135329861</v>
+        <v>135329838</v>
       </c>
       <c r="B101" t="n">
         <v>57975</v>
@@ -11753,10 +11768,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>621226</v>
+        <v>621123</v>
       </c>
       <c r="R101" t="n">
-        <v>7322073</v>
+        <v>7322113</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11788,7 +11803,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11798,7 +11813,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -11834,7 +11849,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135330957</v>
+        <v>135329861</v>
       </c>
       <c r="B102" t="n">
         <v>57975</v>
@@ -11863,24 +11878,19 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>621320</v>
+        <v>621226</v>
       </c>
       <c r="R102" t="n">
-        <v>7322249</v>
+        <v>7322073</v>
       </c>
       <c r="S102" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11909,7 +11919,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11919,12 +11929,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11939,12 +11949,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11955,7 +11965,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135330964</v>
+        <v>135330957</v>
       </c>
       <c r="B103" t="n">
         <v>57975</v>
@@ -11984,27 +11994,24 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>621397</v>
+        <v>621320</v>
       </c>
       <c r="R103" t="n">
-        <v>7322108</v>
+        <v>7322249</v>
       </c>
       <c r="S103" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12033,7 +12040,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12043,12 +12050,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12079,7 +12086,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135330965</v>
+        <v>135330964</v>
       </c>
       <c r="B104" t="n">
         <v>57975</v>
@@ -12122,13 +12129,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>621436</v>
+        <v>621397</v>
       </c>
       <c r="R104" t="n">
-        <v>7322109</v>
+        <v>7322108</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12157,7 +12164,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12167,7 +12174,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -12203,7 +12210,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135330966</v>
+        <v>135330965</v>
       </c>
       <c r="B105" t="n">
         <v>57975</v>
@@ -12236,7 +12243,7 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -12246,13 +12253,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>621459</v>
+        <v>621436</v>
       </c>
       <c r="R105" t="n">
-        <v>7322135</v>
+        <v>7322109</v>
       </c>
       <c r="S105" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12281,7 +12288,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12291,12 +12298,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12327,7 +12334,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135330967</v>
+        <v>135330966</v>
       </c>
       <c r="B106" t="n">
         <v>57975</v>
@@ -12360,7 +12367,7 @@
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -12370,13 +12377,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>621219</v>
+        <v>621459</v>
       </c>
       <c r="R106" t="n">
-        <v>7322131</v>
+        <v>7322135</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12405,7 +12412,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12415,12 +12422,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Spår av födosök</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12451,44 +12458,40 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135330945</v>
+        <v>135330967</v>
       </c>
       <c r="B107" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -12498,13 +12501,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>621163</v>
+        <v>621219</v>
       </c>
       <c r="R107" t="n">
-        <v>7322161</v>
+        <v>7322131</v>
       </c>
       <c r="S107" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12533,7 +12536,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12543,12 +12546,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Uppflygande</t>
+          <t>Spår av födosök</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12579,48 +12582,60 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135326371</v>
+        <v>135330945</v>
       </c>
       <c r="B108" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>621395</v>
+        <v>621163</v>
       </c>
       <c r="R108" t="n">
-        <v>7322009</v>
+        <v>7322161</v>
       </c>
       <c r="S108" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12649,7 +12664,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12659,7 +12674,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12674,12 +12694,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12690,10 +12710,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135326513</v>
+        <v>135326371</v>
       </c>
       <c r="B109" t="n">
-        <v>41606</v>
+        <v>58136</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12701,41 +12721,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>215713</v>
+        <v>103021</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>621171</v>
+        <v>621395</v>
       </c>
       <c r="R109" t="n">
-        <v>7322040</v>
+        <v>7322009</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12764,7 +12780,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12774,7 +12790,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12789,12 +12805,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -12805,45 +12821,49 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135326512</v>
+        <v>135326513</v>
       </c>
       <c r="B110" t="n">
-        <v>98066</v>
+        <v>41606</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221941</v>
+        <v>215713</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>621161</v>
+        <v>621171</v>
       </c>
       <c r="R110" t="n">
-        <v>7322070</v>
+        <v>7322040</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12875,7 +12895,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12885,7 +12905,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12916,48 +12936,48 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135326487</v>
+        <v>135326512</v>
       </c>
       <c r="B111" t="n">
-        <v>78382</v>
+        <v>98066</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228579</v>
+        <v>221941</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>621204</v>
+        <v>621161</v>
       </c>
       <c r="R111" t="n">
-        <v>7322016</v>
+        <v>7322070</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12986,7 +13006,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12996,7 +13016,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13011,12 +13031,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -13027,7 +13047,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135326521</v>
+        <v>135326487</v>
       </c>
       <c r="B112" t="n">
         <v>78382</v>
@@ -13058,17 +13078,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>621266</v>
+        <v>621204</v>
       </c>
       <c r="R112" t="n">
-        <v>7322030</v>
+        <v>7322016</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13097,7 +13117,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13107,7 +13127,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13122,12 +13142,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -13138,7 +13158,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135326526</v>
+        <v>135326521</v>
       </c>
       <c r="B113" t="n">
         <v>78382</v>
@@ -13173,10 +13193,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>621284</v>
+        <v>621266</v>
       </c>
       <c r="R113" t="n">
-        <v>7322006</v>
+        <v>7322030</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13208,7 +13228,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13218,7 +13238,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13249,10 +13269,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135326483</v>
+        <v>135326526</v>
       </c>
       <c r="B114" t="n">
-        <v>79396</v>
+        <v>78382</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13260,37 +13280,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>260591</v>
+        <v>228579</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>621165</v>
+        <v>621284</v>
       </c>
       <c r="R114" t="n">
-        <v>7322074</v>
+        <v>7322006</v>
       </c>
       <c r="S114" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13319,7 +13339,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13329,7 +13349,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13344,12 +13364,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -13360,10 +13380,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135325606</v>
+        <v>135326483</v>
       </c>
       <c r="B115" t="n">
-        <v>92245</v>
+        <v>79396</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13371,37 +13391,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>658</v>
+        <v>260591</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>621546</v>
+        <v>621165</v>
       </c>
       <c r="R115" t="n">
-        <v>7322049</v>
+        <v>7322074</v>
       </c>
       <c r="S115" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13430,7 +13450,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13440,7 +13460,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13455,12 +13475,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -13471,10 +13491,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135323160</v>
+        <v>135325606</v>
       </c>
       <c r="B116" t="n">
-        <v>79452</v>
+        <v>92245</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13482,37 +13502,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>621529</v>
+        <v>621546</v>
       </c>
       <c r="R116" t="n">
-        <v>7322033</v>
+        <v>7322049</v>
       </c>
       <c r="S116" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13541,7 +13561,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13551,7 +13571,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13566,12 +13586,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -13582,32 +13602,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135323154</v>
+        <v>135323160</v>
       </c>
       <c r="B117" t="n">
-        <v>92795</v>
+        <v>79452</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>918</v>
+        <v>864</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13617,13 +13637,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>621513</v>
+        <v>621529</v>
       </c>
       <c r="R117" t="n">
-        <v>7322084</v>
+        <v>7322033</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13652,7 +13672,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13662,7 +13682,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13693,7 +13713,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135323161</v>
+        <v>135323154</v>
       </c>
       <c r="B118" t="n">
         <v>92795</v>
@@ -13728,10 +13748,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>621535</v>
+        <v>621513</v>
       </c>
       <c r="R118" t="n">
-        <v>7322033</v>
+        <v>7322084</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13763,7 +13783,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13773,7 +13793,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13804,7 +13824,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135325607</v>
+        <v>135323161</v>
       </c>
       <c r="B119" t="n">
         <v>92795</v>
@@ -13835,14 +13855,14 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>621551</v>
+        <v>621535</v>
       </c>
       <c r="R119" t="n">
-        <v>7322047</v>
+        <v>7322033</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13874,7 +13894,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13884,7 +13904,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13899,12 +13919,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -13915,7 +13935,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135325611</v>
+        <v>135325607</v>
       </c>
       <c r="B120" t="n">
         <v>92795</v>
@@ -13950,13 +13970,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>621536</v>
+        <v>621551</v>
       </c>
       <c r="R120" t="n">
-        <v>7322045</v>
+        <v>7322047</v>
       </c>
       <c r="S120" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13985,7 +14005,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13995,7 +14015,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14026,32 +14046,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135325610</v>
+        <v>135325611</v>
       </c>
       <c r="B121" t="n">
-        <v>91970</v>
+        <v>92795</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14061,13 +14081,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>621539</v>
+        <v>621536</v>
       </c>
       <c r="R121" t="n">
-        <v>7322038</v>
+        <v>7322045</v>
       </c>
       <c r="S121" t="n">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14096,7 +14116,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14106,7 +14126,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14137,10 +14157,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135325608</v>
+        <v>135325610</v>
       </c>
       <c r="B122" t="n">
-        <v>91974</v>
+        <v>91970</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14148,21 +14168,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14172,13 +14192,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>621550</v>
+        <v>621539</v>
       </c>
       <c r="R122" t="n">
-        <v>7322047</v>
+        <v>7322038</v>
       </c>
       <c r="S122" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14207,7 +14227,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14217,7 +14237,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14248,10 +14268,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135325601</v>
+        <v>135325608</v>
       </c>
       <c r="B123" t="n">
-        <v>83222</v>
+        <v>91974</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14259,21 +14279,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14283,13 +14303,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>621522</v>
+        <v>621550</v>
       </c>
       <c r="R123" t="n">
-        <v>7322095</v>
+        <v>7322047</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14318,7 +14338,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14328,12 +14348,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Cinnoberflamlav</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14364,7 +14379,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135325603</v>
+        <v>135325601</v>
       </c>
       <c r="B124" t="n">
         <v>83222</v>
@@ -14399,10 +14414,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>621524</v>
+        <v>621522</v>
       </c>
       <c r="R124" t="n">
-        <v>7322055</v>
+        <v>7322095</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14434,7 +14449,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14444,7 +14459,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Cinnoberflamlav</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14475,48 +14495,48 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135323155</v>
+        <v>135325603</v>
       </c>
       <c r="B125" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>621518</v>
+        <v>621524</v>
       </c>
       <c r="R125" t="n">
-        <v>7322064</v>
+        <v>7322055</v>
       </c>
       <c r="S125" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14570,12 +14590,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -14586,48 +14606,48 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135325602</v>
+        <v>135323155</v>
       </c>
       <c r="B126" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>621515</v>
+        <v>621518</v>
       </c>
       <c r="R126" t="n">
-        <v>7322081</v>
+        <v>7322064</v>
       </c>
       <c r="S126" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14656,7 +14676,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14666,7 +14686,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14681,12 +14701,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -14697,7 +14717,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>135325609</v>
+        <v>135325602</v>
       </c>
       <c r="B127" t="n">
         <v>83358</v>
@@ -14732,13 +14752,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>621545</v>
+        <v>621515</v>
       </c>
       <c r="R127" t="n">
-        <v>7322048</v>
+        <v>7322081</v>
       </c>
       <c r="S127" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14767,7 +14787,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14777,7 +14797,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14808,48 +14828,48 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>135323153</v>
+        <v>135325609</v>
       </c>
       <c r="B128" t="n">
-        <v>78731</v>
+        <v>83358</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6443</v>
+        <v>6440</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>621513</v>
+        <v>621545</v>
       </c>
       <c r="R128" t="n">
-        <v>7322084</v>
+        <v>7322048</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14878,7 +14898,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14888,12 +14908,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>På torr grangren</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14908,15 +14923,131 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>135323153</v>
+      </c>
+      <c r="B129" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Sotlav</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Acolium inquinans</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Skornjamyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>621513</v>
+      </c>
+      <c r="R129" t="n">
+        <v>7322084</v>
+      </c>
+      <c r="S129" t="n">
+        <v>5</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>På torr grangren</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
           <t>Cajsa Björkén</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
+      <c r="AX129" t="inlineStr">
         <is>
           <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
-      <c r="AY128" t="inlineStr">
+      <c r="AY129" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">

--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">

--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">

--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Martin Axegård, Christina Boyd, Laura de Jong</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">

--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Martin Axegård, Christina Boyd, Laura de Jong</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">

--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY134"/>
+  <dimension ref="A1:AZ134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323944</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322207</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322208</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323158</t>
         </is>
       </c>
     </row>
@@ -1251,6 +1276,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135360046</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1362,6 +1392,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323166</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1473,6 +1508,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323172</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,6 +1624,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330954</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1695,6 +1740,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322209</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1806,6 +1856,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323170</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1917,6 +1972,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323174</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2024,6 +2084,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323544</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2155,6 +2220,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323940</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2281,6 +2351,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323942</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2392,6 +2467,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325614</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2503,6 +2583,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325615</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2614,6 +2699,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326363</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2725,6 +2815,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326494</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2836,6 +2931,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330944</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2947,6 +3047,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330962</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3058,6 +3163,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323152</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3169,6 +3279,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326516</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3280,6 +3395,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329849</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3391,6 +3511,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329856</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3500,6 +3625,11 @@
       <c r="AY26" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329858</t>
         </is>
       </c>
     </row>
@@ -3617,6 +3747,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359947</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3728,6 +3863,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325596</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3839,6 +3979,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325619</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3950,6 +4095,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325628</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4061,6 +4211,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326490</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4172,6 +4327,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330955</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4283,6 +4443,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323157</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4390,6 +4555,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323537</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4497,6 +4667,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323538</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4608,6 +4783,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325613</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4719,6 +4899,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325621</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4830,6 +5015,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326368</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4946,6 +5136,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329807</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5053,6 +5248,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323539</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5164,6 +5364,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325617</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5275,6 +5480,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325631</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5386,6 +5596,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326370</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5497,6 +5712,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326374</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5608,6 +5828,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326488</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5719,6 +5944,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326491</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5830,6 +6060,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326493</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5941,6 +6176,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326528</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6052,6 +6292,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330949</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6163,6 +6408,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330959</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6279,6 +6529,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329809</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6390,6 +6645,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330960</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6501,6 +6761,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330963</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6627,6 +6892,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323943</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6738,6 +7008,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323148</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6849,6 +7124,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323159</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6960,6 +7240,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325599</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7071,6 +7356,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325625</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7182,6 +7472,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326511</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7293,6 +7588,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326520</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7404,6 +7704,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329841</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7515,6 +7820,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326367</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7626,6 +7936,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326373</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7737,6 +8052,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326376</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7848,6 +8168,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323164</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7955,6 +8280,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323540</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8064,6 +8394,11 @@
       <c r="AY67" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330951</t>
         </is>
       </c>
     </row>
@@ -8197,6 +8532,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323941</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8308,6 +8648,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323167</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8415,6 +8760,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323542</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8526,6 +8876,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323149</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8637,6 +8992,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323173</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8748,6 +9108,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325598</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8859,6 +9224,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325620</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8970,6 +9340,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325622</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9081,6 +9456,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326492</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9192,6 +9572,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326518</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9303,6 +9688,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329852</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9414,6 +9804,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329854</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9525,6 +9920,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326484</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9636,6 +10036,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323162</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9747,6 +10152,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323147</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9858,6 +10268,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323151</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9969,6 +10384,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325600</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10080,6 +10500,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325618</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10191,6 +10616,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325624</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10302,6 +10732,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326486</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10413,6 +10848,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326495</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10524,6 +10964,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326523</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10635,6 +11080,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329844</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10746,6 +11196,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322206</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10857,6 +11312,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323169</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10968,6 +11428,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325627</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11079,6 +11544,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325629</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11195,6 +11665,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329808</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11306,6 +11781,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330953</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11417,6 +11897,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325633</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11528,6 +12013,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330943</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11639,6 +12129,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330946</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11755,6 +12250,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323175</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11867,6 +12367,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323536</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11991,6 +12496,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326366</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12115,6 +12625,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326496</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12239,6 +12754,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326497</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12355,6 +12875,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329838</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12471,6 +12996,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329861</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12592,6 +13122,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330957</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12716,6 +13251,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330964</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12840,6 +13380,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330965</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12964,6 +13509,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330966</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13088,6 +13638,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330967</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13216,6 +13771,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330945</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13327,6 +13887,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326371</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13457,6 +14022,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323938</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13572,6 +14142,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326513</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13683,6 +14258,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326512</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13794,6 +14374,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326487</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13905,6 +14490,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326521</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14016,6 +14606,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326526</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14127,6 +14722,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326483</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14238,6 +14838,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325606</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14349,6 +14954,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323160</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14460,6 +15070,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323154</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14571,6 +15186,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323161</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14682,6 +15302,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325607</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14793,6 +15418,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325611</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14904,6 +15534,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325610</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15015,6 +15650,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325608</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15131,6 +15771,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325601</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15242,6 +15887,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325603</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15353,6 +16003,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323155</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15464,6 +16119,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325602</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15575,6 +16235,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325609</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15691,8 +16356,148 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323153</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135323944</v>
       </c>
       <c r="B2" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>135322207</v>
       </c>
       <c r="B3" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135322208</v>
       </c>
       <c r="B4" t="n">
-        <v>92201</v>
+        <v>92243</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>135323158</v>
       </c>
       <c r="B5" t="n">
-        <v>92201</v>
+        <v>92243</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>135360046</v>
       </c>
       <c r="B6" t="n">
-        <v>92201</v>
+        <v>92243</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>135323166</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>135323172</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>135330954</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>135322209</v>
       </c>
       <c r="B10" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>135323170</v>
       </c>
       <c r="B11" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135323174</v>
       </c>
       <c r="B12" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>135323544</v>
       </c>
       <c r="B13" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>135323940</v>
       </c>
       <c r="B14" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135323942</v>
       </c>
       <c r="B15" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>135325614</v>
       </c>
       <c r="B16" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135325615</v>
       </c>
       <c r="B17" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>135326363</v>
       </c>
       <c r="B18" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>135326494</v>
       </c>
       <c r="B19" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>135330944</v>
       </c>
       <c r="B20" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135330962</v>
       </c>
       <c r="B21" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135323152</v>
       </c>
       <c r="B22" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>135326516</v>
       </c>
       <c r="B23" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>135329849</v>
       </c>
       <c r="B24" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>135329856</v>
       </c>
       <c r="B25" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>135329858</v>
       </c>
       <c r="B26" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>135359947</v>
       </c>
       <c r="B27" t="n">
-        <v>92689</v>
+        <v>92731</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>135325596</v>
       </c>
       <c r="B28" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>135325619</v>
       </c>
       <c r="B29" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>135325628</v>
       </c>
       <c r="B30" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>135326490</v>
       </c>
       <c r="B31" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>135330955</v>
       </c>
       <c r="B32" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>135323157</v>
       </c>
       <c r="B33" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>135323537</v>
       </c>
       <c r="B34" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>135323538</v>
       </c>
       <c r="B35" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>135325613</v>
       </c>
       <c r="B36" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>135325621</v>
       </c>
       <c r="B37" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>135326368</v>
       </c>
       <c r="B38" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>135329807</v>
       </c>
       <c r="B39" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>135323539</v>
       </c>
       <c r="B40" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>135325617</v>
       </c>
       <c r="B41" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>135325631</v>
       </c>
       <c r="B42" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>135326370</v>
       </c>
       <c r="B43" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>135326374</v>
       </c>
       <c r="B44" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>135326488</v>
       </c>
       <c r="B45" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>135326491</v>
       </c>
       <c r="B46" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>135326493</v>
       </c>
       <c r="B47" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>135326528</v>
       </c>
       <c r="B48" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>135330949</v>
       </c>
       <c r="B49" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>135330959</v>
       </c>
       <c r="B50" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>135329809</v>
       </c>
       <c r="B51" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>135330960</v>
       </c>
       <c r="B52" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>135330963</v>
       </c>
       <c r="B53" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>135323943</v>
       </c>
       <c r="B54" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>135323148</v>
       </c>
       <c r="B55" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>135323159</v>
       </c>
       <c r="B56" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>135325599</v>
       </c>
       <c r="B57" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>135325625</v>
       </c>
       <c r="B58" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>135326511</v>
       </c>
       <c r="B59" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>135326520</v>
       </c>
       <c r="B60" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>135329841</v>
       </c>
       <c r="B61" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>135326367</v>
       </c>
       <c r="B62" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>135326373</v>
       </c>
       <c r="B63" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>135326376</v>
       </c>
       <c r="B64" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>135323164</v>
       </c>
       <c r="B65" t="n">
-        <v>92167</v>
+        <v>92209</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>135323540</v>
       </c>
       <c r="B66" t="n">
-        <v>92318</v>
+        <v>92360</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>135330951</v>
       </c>
       <c r="B67" t="n">
-        <v>92318</v>
+        <v>92360</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>135323941</v>
       </c>
       <c r="B68" t="n">
-        <v>96678</v>
+        <v>96722</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>135323167</v>
       </c>
       <c r="B69" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>135323542</v>
       </c>
       <c r="B70" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>135323149</v>
       </c>
       <c r="B71" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>135323173</v>
       </c>
       <c r="B72" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>135325598</v>
       </c>
       <c r="B73" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>135325620</v>
       </c>
       <c r="B74" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>135325622</v>
       </c>
       <c r="B75" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>135326492</v>
       </c>
       <c r="B76" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>135326518</v>
       </c>
       <c r="B77" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>135329852</v>
       </c>
       <c r="B78" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>135329854</v>
       </c>
       <c r="B79" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>135326484</v>
       </c>
       <c r="B80" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>135323162</v>
       </c>
       <c r="B81" t="n">
-        <v>83341</v>
+        <v>83381</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>135323147</v>
       </c>
       <c r="B82" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>135323151</v>
       </c>
       <c r="B83" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>135325600</v>
       </c>
       <c r="B84" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>135325618</v>
       </c>
       <c r="B85" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>135325624</v>
       </c>
       <c r="B86" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>135326486</v>
       </c>
       <c r="B87" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>135326495</v>
       </c>
       <c r="B88" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>135326523</v>
       </c>
       <c r="B89" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>135329844</v>
       </c>
       <c r="B90" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>135322206</v>
       </c>
       <c r="B91" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>135323169</v>
       </c>
       <c r="B92" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>135325627</v>
       </c>
       <c r="B93" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>135325629</v>
       </c>
       <c r="B94" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>135329808</v>
       </c>
       <c r="B95" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>135330953</v>
       </c>
       <c r="B96" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>135325633</v>
       </c>
       <c r="B97" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>135330943</v>
       </c>
       <c r="B98" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>135330946</v>
       </c>
       <c r="B99" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>135323175</v>
       </c>
       <c r="B100" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>135323536</v>
       </c>
       <c r="B101" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>135326366</v>
       </c>
       <c r="B102" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>135326496</v>
       </c>
       <c r="B103" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>135326497</v>
       </c>
       <c r="B104" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>135329838</v>
       </c>
       <c r="B105" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>135329861</v>
       </c>
       <c r="B106" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>135330957</v>
       </c>
       <c r="B107" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>135330964</v>
       </c>
       <c r="B108" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>135330965</v>
       </c>
       <c r="B109" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>135330966</v>
       </c>
       <c r="B110" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>135330967</v>
       </c>
       <c r="B111" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>135330945</v>
       </c>
       <c r="B112" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>135326371</v>
       </c>
       <c r="B113" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>135326513</v>
       </c>
       <c r="B115" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>135326512</v>
       </c>
       <c r="B116" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>135326487</v>
       </c>
       <c r="B117" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>135326521</v>
       </c>
       <c r="B118" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>135326526</v>
       </c>
       <c r="B119" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>135326483</v>
       </c>
       <c r="B120" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>135325606</v>
       </c>
       <c r="B121" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>135323160</v>
       </c>
       <c r="B122" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>135323154</v>
       </c>
       <c r="B123" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>135323161</v>
       </c>
       <c r="B124" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>135325607</v>
       </c>
       <c r="B125" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>135325611</v>
       </c>
       <c r="B126" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>135325610</v>
       </c>
       <c r="B127" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>135325608</v>
       </c>
       <c r="B128" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>135325601</v>
       </c>
       <c r="B129" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>135325603</v>
       </c>
       <c r="B130" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>135323155</v>
       </c>
       <c r="B131" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>135325602</v>
       </c>
       <c r="B132" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>135325609</v>
       </c>
       <c r="B133" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>135323153</v>
       </c>
       <c r="B134" t="n">
-        <v>78731</v>
+        <v>78769</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135323944</v>
       </c>
       <c r="B2" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>135322207</v>
       </c>
       <c r="B3" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135322208</v>
       </c>
       <c r="B4" t="n">
-        <v>92243</v>
+        <v>92270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>135323158</v>
       </c>
       <c r="B5" t="n">
-        <v>92243</v>
+        <v>92270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>135360046</v>
       </c>
       <c r="B6" t="n">
-        <v>92243</v>
+        <v>92270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>135323166</v>
       </c>
       <c r="B7" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>135323172</v>
       </c>
       <c r="B8" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>135330954</v>
       </c>
       <c r="B9" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>135322209</v>
       </c>
       <c r="B10" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>135323170</v>
       </c>
       <c r="B11" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135323174</v>
       </c>
       <c r="B12" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>135323544</v>
       </c>
       <c r="B13" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>135323940</v>
       </c>
       <c r="B14" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135323942</v>
       </c>
       <c r="B15" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>135325614</v>
       </c>
       <c r="B16" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135325615</v>
       </c>
       <c r="B17" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>135326363</v>
       </c>
       <c r="B18" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>135326494</v>
       </c>
       <c r="B19" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>135330944</v>
       </c>
       <c r="B20" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135330962</v>
       </c>
       <c r="B21" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135323152</v>
       </c>
       <c r="B22" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>135326516</v>
       </c>
       <c r="B23" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>135329849</v>
       </c>
       <c r="B24" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>135329856</v>
       </c>
       <c r="B25" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>135329858</v>
       </c>
       <c r="B26" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>135359947</v>
       </c>
       <c r="B27" t="n">
-        <v>92731</v>
+        <v>92758</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>135325596</v>
       </c>
       <c r="B28" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>135325619</v>
       </c>
       <c r="B29" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>135325628</v>
       </c>
       <c r="B30" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>135326490</v>
       </c>
       <c r="B31" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>135330955</v>
       </c>
       <c r="B32" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>135323157</v>
       </c>
       <c r="B33" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>135323537</v>
       </c>
       <c r="B34" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>135323538</v>
       </c>
       <c r="B35" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>135325613</v>
       </c>
       <c r="B36" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>135325621</v>
       </c>
       <c r="B37" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>135326368</v>
       </c>
       <c r="B38" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>135329807</v>
       </c>
       <c r="B39" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>135323539</v>
       </c>
       <c r="B40" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>135325617</v>
       </c>
       <c r="B41" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>135325631</v>
       </c>
       <c r="B42" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>135326370</v>
       </c>
       <c r="B43" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>135326374</v>
       </c>
       <c r="B44" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>135326488</v>
       </c>
       <c r="B45" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>135326491</v>
       </c>
       <c r="B46" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>135326493</v>
       </c>
       <c r="B47" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>135326528</v>
       </c>
       <c r="B48" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>135330949</v>
       </c>
       <c r="B49" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>135330959</v>
       </c>
       <c r="B50" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>135329809</v>
       </c>
       <c r="B51" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>135330960</v>
       </c>
       <c r="B52" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>135330963</v>
       </c>
       <c r="B53" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>135323943</v>
       </c>
       <c r="B54" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>135323148</v>
       </c>
       <c r="B55" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>135323159</v>
       </c>
       <c r="B56" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>135325599</v>
       </c>
       <c r="B57" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>135325625</v>
       </c>
       <c r="B58" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>135326511</v>
       </c>
       <c r="B59" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>135326520</v>
       </c>
       <c r="B60" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>135329841</v>
       </c>
       <c r="B61" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>135326367</v>
       </c>
       <c r="B62" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>135326373</v>
       </c>
       <c r="B63" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>135326376</v>
       </c>
       <c r="B64" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>135323164</v>
       </c>
       <c r="B65" t="n">
-        <v>92209</v>
+        <v>92236</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>135323540</v>
       </c>
       <c r="B66" t="n">
-        <v>92360</v>
+        <v>92387</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>135330951</v>
       </c>
       <c r="B67" t="n">
-        <v>92360</v>
+        <v>92387</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>135323941</v>
       </c>
       <c r="B68" t="n">
-        <v>96722</v>
+        <v>96749</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>135323167</v>
       </c>
       <c r="B69" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>135323542</v>
       </c>
       <c r="B70" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>135323149</v>
       </c>
       <c r="B71" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>135323173</v>
       </c>
       <c r="B72" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>135325598</v>
       </c>
       <c r="B73" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>135325620</v>
       </c>
       <c r="B74" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>135325622</v>
       </c>
       <c r="B75" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>135326492</v>
       </c>
       <c r="B76" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>135326518</v>
       </c>
       <c r="B77" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>135329852</v>
       </c>
       <c r="B78" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>135329854</v>
       </c>
       <c r="B79" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>135326484</v>
       </c>
       <c r="B80" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>135323162</v>
       </c>
       <c r="B81" t="n">
-        <v>83381</v>
+        <v>83408</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>135323147</v>
       </c>
       <c r="B82" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>135323151</v>
       </c>
       <c r="B83" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>135325600</v>
       </c>
       <c r="B84" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>135325618</v>
       </c>
       <c r="B85" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>135325624</v>
       </c>
       <c r="B86" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>135326486</v>
       </c>
       <c r="B87" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>135326495</v>
       </c>
       <c r="B88" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>135326523</v>
       </c>
       <c r="B89" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>135329844</v>
       </c>
       <c r="B90" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>135322206</v>
       </c>
       <c r="B91" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>135323169</v>
       </c>
       <c r="B92" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>135325627</v>
       </c>
       <c r="B93" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>135325629</v>
       </c>
       <c r="B94" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>135329808</v>
       </c>
       <c r="B95" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>135330953</v>
       </c>
       <c r="B96" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>135325633</v>
       </c>
       <c r="B97" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>135330943</v>
       </c>
       <c r="B98" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>135330946</v>
       </c>
       <c r="B99" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>135326512</v>
       </c>
       <c r="B116" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>135326487</v>
       </c>
       <c r="B117" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>135326521</v>
       </c>
       <c r="B118" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>135326526</v>
       </c>
       <c r="B119" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>135326483</v>
       </c>
       <c r="B120" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>135325606</v>
       </c>
       <c r="B121" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>135323160</v>
       </c>
       <c r="B122" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>135323154</v>
       </c>
       <c r="B123" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>135323161</v>
       </c>
       <c r="B124" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>135325607</v>
       </c>
       <c r="B125" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>135325611</v>
       </c>
       <c r="B126" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>135325610</v>
       </c>
       <c r="B127" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>135325608</v>
       </c>
       <c r="B128" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>135325601</v>
       </c>
       <c r="B129" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>135325603</v>
       </c>
       <c r="B130" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>135323155</v>
       </c>
       <c r="B131" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>135325602</v>
       </c>
       <c r="B132" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>135325609</v>
       </c>
       <c r="B133" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>135323153</v>
       </c>
       <c r="B134" t="n">
-        <v>78769</v>
+        <v>78796</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">

--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">

--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135323944</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>135322207</v>
       </c>
       <c r="B3" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135322208</v>
       </c>
       <c r="B4" t="n">
-        <v>92275</v>
+        <v>92277</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>135323158</v>
       </c>
       <c r="B5" t="n">
-        <v>92275</v>
+        <v>92277</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>135360046</v>
       </c>
       <c r="B6" t="n">
-        <v>92275</v>
+        <v>92277</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>135322209</v>
       </c>
       <c r="B10" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>135323170</v>
       </c>
       <c r="B11" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135323174</v>
       </c>
       <c r="B12" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>135323544</v>
       </c>
       <c r="B13" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>135323940</v>
       </c>
       <c r="B14" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135323942</v>
       </c>
       <c r="B15" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>135325614</v>
       </c>
       <c r="B16" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135325615</v>
       </c>
       <c r="B17" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>135326363</v>
       </c>
       <c r="B18" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>135326494</v>
       </c>
       <c r="B19" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>135330944</v>
       </c>
       <c r="B20" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135330962</v>
       </c>
       <c r="B21" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>135359947</v>
       </c>
       <c r="B27" t="n">
-        <v>92763</v>
+        <v>92765</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>135325596</v>
       </c>
       <c r="B28" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>135325619</v>
       </c>
       <c r="B29" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>135325628</v>
       </c>
       <c r="B30" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>135326490</v>
       </c>
       <c r="B31" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>135330955</v>
       </c>
       <c r="B32" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>135323157</v>
       </c>
       <c r="B33" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>135323537</v>
       </c>
       <c r="B34" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>135323538</v>
       </c>
       <c r="B35" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>135325613</v>
       </c>
       <c r="B36" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>135325621</v>
       </c>
       <c r="B37" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>135326368</v>
       </c>
       <c r="B38" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>135329807</v>
       </c>
       <c r="B39" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>135323539</v>
       </c>
       <c r="B40" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>135325617</v>
       </c>
       <c r="B41" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>135325631</v>
       </c>
       <c r="B42" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>135326370</v>
       </c>
       <c r="B43" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>135326374</v>
       </c>
       <c r="B44" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>135326488</v>
       </c>
       <c r="B45" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>135326491</v>
       </c>
       <c r="B46" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>135326493</v>
       </c>
       <c r="B47" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>135326528</v>
       </c>
       <c r="B48" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>135330949</v>
       </c>
       <c r="B49" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>135330959</v>
       </c>
       <c r="B50" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>135329809</v>
       </c>
       <c r="B51" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>135330960</v>
       </c>
       <c r="B52" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>135330963</v>
       </c>
       <c r="B53" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>135323943</v>
       </c>
       <c r="B54" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>135326367</v>
       </c>
       <c r="B62" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>135326373</v>
       </c>
       <c r="B63" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>135326376</v>
       </c>
       <c r="B64" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>135323164</v>
       </c>
       <c r="B65" t="n">
-        <v>92241</v>
+        <v>92243</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>135323540</v>
       </c>
       <c r="B66" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>135330951</v>
       </c>
       <c r="B67" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>135323941</v>
       </c>
       <c r="B68" t="n">
-        <v>96754</v>
+        <v>96756</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>135323167</v>
       </c>
       <c r="B69" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>135323542</v>
       </c>
       <c r="B70" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>135326512</v>
       </c>
       <c r="B116" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>135325606</v>
       </c>
       <c r="B121" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>135323154</v>
       </c>
       <c r="B123" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>135323161</v>
       </c>
       <c r="B124" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>135325607</v>
       </c>
       <c r="B125" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>135325611</v>
       </c>
       <c r="B126" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>135325610</v>
       </c>
       <c r="B127" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>135325608</v>
       </c>
       <c r="B128" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">

--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">

--- a/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
+++ b/artfynd/Maskaure Skornjamyran avvanm, 11,2 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135323944</v>
       </c>
       <c r="B2" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>135323940</v>
       </c>
       <c r="B14" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135323942</v>
       </c>
       <c r="B15" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>135323943</v>
       </c>
       <c r="B54" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>135323941</v>
       </c>
       <c r="B68" t="n">
-        <v>96756</v>
+        <v>96773</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>135323938</v>
       </c>
       <c r="B114" t="n">
-        <v>6286</v>
+        <v>6288</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
